--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\SourceFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE13E97-D59A-4D97-809C-3BC829E6B926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3065D476-8D49-42AC-8402-5325A9756135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="1905" windowWidth="19995" windowHeight="10125" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="1800" windowWidth="20115" windowHeight="12015" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -844,6 +844,7 @@
       <sheetName val="The Mountain-hold"/>
       <sheetName val="Return to Carn Dûm"/>
       <sheetName val="Corsairs of Umbar"/>
+      <sheetName val="The Legacy of Morgoth"/>
       <sheetName val="&lt;template&gt;"/>
     </sheetNames>
     <sheetDataSet>
@@ -1645,6 +1646,7 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10866,7 +10868,7 @@
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="55" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
@@ -11150,22 +11152,22 @@
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1879326410</v>
+        <v>1879326399</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
         <v>154</v>
       </c>
       <c r="G3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="L3" t="s">
         <v>151</v>
@@ -11175,11 +11177,11 @@
       </c>
       <c r="R3" t="str">
         <f t="shared" ref="R3:R9" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
-        <v xml:space="preserve">  [2] = {["ID"] = 1879326410; }; -- Quest of the Court of Anárion -- Tier 1</v>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879326399; }; -- Quest of the Court of Anárion -- Tier 3</v>
       </c>
       <c r="S3" s="1" t="str">
         <f t="shared" ref="S3:S9" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
-        <v xml:space="preserve">  [2] = {["ID"] = 1879326410; ["SAVE_INDEX"] = 2; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; };</v>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879326399; ["SAVE_INDEX"] = 4; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; };</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T9" si="3">ROW()-1</f>
@@ -11191,11 +11193,11 @@
       </c>
       <c r="V3" t="str">
         <f t="shared" ref="V3:V9" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879326410; </v>
+        <v xml:space="preserve">["ID"] = 1879326399; </v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W9" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879326410; </v>
+        <v xml:space="preserve">["ID"] = 1879326399; </v>
       </c>
       <c r="X3" t="str">
         <f t="shared" ref="X3:X9" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
@@ -11203,7 +11205,7 @@
       </c>
       <c r="Y3" s="1" t="str">
         <f t="shared" ref="Y3:Y9" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
-        <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
+        <v xml:space="preserve">["SAVE_INDEX"] = 4; </v>
       </c>
       <c r="Z3">
         <f>VLOOKUP(D3,[1]Type!A$2:B$18,2,FALSE)</f>
@@ -11267,7 +11269,7 @@
       </c>
       <c r="AO3" t="str">
         <f t="shared" ref="AO3:AO9" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; </v>
       </c>
       <c r="AP3" t="str">
         <f t="shared" ref="AP3:AP9" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
@@ -11275,11 +11277,11 @@
       </c>
       <c r="AQ3" t="str">
         <f t="shared" ref="AQ3:AQ9" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; </v>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; </v>
       </c>
       <c r="AR3" t="str">
         <f t="shared" ref="AR3:AR9" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
-        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; </v>
+        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; </v>
       </c>
       <c r="AS3" t="str">
         <f t="shared" ref="AS3:AS9" si="25">CONCATENATE("};")</f>
@@ -11426,22 +11428,22 @@
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1879326399</v>
+        <v>1879326410</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
         <v>154</v>
       </c>
       <c r="G5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L5" t="s">
         <v>151</v>
@@ -11451,11 +11453,11 @@
       </c>
       <c r="R5" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879326399; }; -- Quest of the Court of Anárion -- Tier 3</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; }; -- Quest of the Court of Anárion -- Tier 1</v>
       </c>
       <c r="S5" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879326399; ["SAVE_INDEX"] = 4; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; };</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; ["SAVE_INDEX"] = 2; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; };</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
@@ -11467,11 +11469,11 @@
       </c>
       <c r="V5" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">["ID"] = 1879326399; </v>
+        <v xml:space="preserve">["ID"] = 1879326410; </v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">["ID"] = 1879326399; </v>
+        <v xml:space="preserve">["ID"] = 1879326410; </v>
       </c>
       <c r="X5" t="str">
         <f t="shared" si="7"/>
@@ -11479,7 +11481,7 @@
       </c>
       <c r="Y5" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">["SAVE_INDEX"] = 4; </v>
+        <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="Z5">
         <f>VLOOKUP(D5,[1]Type!A$2:B$18,2,FALSE)</f>
@@ -11543,7 +11545,7 @@
       </c>
       <c r="AO5" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; </v>
       </c>
       <c r="AP5" t="str">
         <f t="shared" si="22"/>
@@ -11551,11 +11553,11 @@
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="23"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; </v>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; </v>
       </c>
       <c r="AR5" t="str">
         <f t="shared" si="24"/>
-        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; </v>
+        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; </v>
       </c>
       <c r="AS5" t="str">
         <f t="shared" si="25"/>
@@ -11564,22 +11566,22 @@
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1879326404</v>
+        <v>1879326398</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
         <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L6" t="s">
         <v>159</v>
@@ -11589,11 +11591,11 @@
       </c>
       <c r="R6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879326404; }; -- Quest of the Palace of Eldacar -- Tier 1</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879326398; }; -- Quest of the Palace of Eldacar -- Tier 3</v>
       </c>
       <c r="S6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879326404; ["SAVE_INDEX"] = 5; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; };</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879326398; ["SAVE_INDEX"] = 7; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; };</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
@@ -11605,11 +11607,11 @@
       </c>
       <c r="V6" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">["ID"] = 1879326404; </v>
+        <v xml:space="preserve">["ID"] = 1879326398; </v>
       </c>
       <c r="W6" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">["ID"] = 1879326404; </v>
+        <v xml:space="preserve">["ID"] = 1879326398; </v>
       </c>
       <c r="X6" t="str">
         <f t="shared" si="7"/>
@@ -11617,7 +11619,7 @@
       </c>
       <c r="Y6" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">["SAVE_INDEX"] = 5; </v>
+        <v xml:space="preserve">["SAVE_INDEX"] = 7; </v>
       </c>
       <c r="Z6">
         <f>VLOOKUP(D6,[1]Type!A$2:B$18,2,FALSE)</f>
@@ -11681,7 +11683,7 @@
       </c>
       <c r="AO6" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; </v>
       </c>
       <c r="AP6" t="str">
         <f t="shared" si="22"/>
@@ -11689,11 +11691,11 @@
       </c>
       <c r="AQ6" t="str">
         <f t="shared" si="23"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; </v>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; </v>
       </c>
       <c r="AR6" t="str">
         <f t="shared" si="24"/>
-        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; </v>
+        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; </v>
       </c>
       <c r="AS6" t="str">
         <f t="shared" si="25"/>
@@ -11840,22 +11842,22 @@
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1879326398</v>
+        <v>1879326404</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
         <v>154</v>
       </c>
       <c r="G8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L8" t="s">
         <v>159</v>
@@ -11865,11 +11867,11 @@
       </c>
       <c r="R8" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879326398; }; -- Quest of the Palace of Eldacar -- Tier 3</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; }; -- Quest of the Palace of Eldacar -- Tier 1</v>
       </c>
       <c r="S8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879326398; ["SAVE_INDEX"] = 7; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; };</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; ["SAVE_INDEX"] = 5; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; };</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
@@ -11881,11 +11883,11 @@
       </c>
       <c r="V8" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">["ID"] = 1879326398; </v>
+        <v xml:space="preserve">["ID"] = 1879326404; </v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">["ID"] = 1879326398; </v>
+        <v xml:space="preserve">["ID"] = 1879326404; </v>
       </c>
       <c r="X8" t="str">
         <f t="shared" si="7"/>
@@ -11893,7 +11895,7 @@
       </c>
       <c r="Y8" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">["SAVE_INDEX"] = 7; </v>
+        <v xml:space="preserve">["SAVE_INDEX"] = 5; </v>
       </c>
       <c r="Z8">
         <f>VLOOKUP(D8,[1]Type!A$2:B$18,2,FALSE)</f>
@@ -11957,7 +11959,7 @@
       </c>
       <c r="AO8" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; </v>
       </c>
       <c r="AP8" t="str">
         <f t="shared" si="22"/>
@@ -11965,11 +11967,11 @@
       </c>
       <c r="AQ8" t="str">
         <f t="shared" si="23"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; </v>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; </v>
       </c>
       <c r="AR8" t="str">
         <f t="shared" si="24"/>
-        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; </v>
+        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; </v>
       </c>
       <c r="AS8" t="str">
         <f t="shared" si="25"/>
@@ -12281,8 +12283,9 @@
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P8">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3065D476-8D49-42AC-8402-5325A9756135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B3A80-CB90-4BA2-B860-A8A0C987AEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="1800" windowWidth="20115" windowHeight="12015" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23085" yWindow="2475" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="209">
   <si>
     <t>Save Index</t>
   </si>
@@ -632,28 +632,40 @@
     <t>Title: Steward of the Ettenmoors</t>
   </si>
   <si>
-    <t>Title: Servant of Shadow</t>
-  </si>
-  <si>
     <t>Title: Preserver of Order</t>
   </si>
   <si>
     <t>- Monster Player Reward Season 1 -</t>
   </si>
   <si>
-    <t>Title: Angmar's Enforcer</t>
-  </si>
-  <si>
-    <t>Title: Abomination</t>
-  </si>
-  <si>
     <t>Title: Exemplar</t>
   </si>
   <si>
-    <t>Title: Scourge of the Ettenmoors</t>
-  </si>
-  <si>
     <t>Limited Time Only</t>
+  </si>
+  <si>
+    <t>- Season of the Nemesis -</t>
+  </si>
+  <si>
+    <t>Title: Benevolence Incarnate</t>
+  </si>
+  <si>
+    <t>Title: The Respected Voice</t>
+  </si>
+  <si>
+    <t>- Season of Scorn -</t>
+  </si>
+  <si>
+    <t>- Season of Spirit -</t>
+  </si>
+  <si>
+    <t>- Season of Malice -</t>
+  </si>
+  <si>
+    <t>Title: The Spirit's Guide</t>
+  </si>
+  <si>
+    <t>Title: Bearer of Truth</t>
   </si>
 </sst>
 </file>
@@ -703,11 +715,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8273,17 +8286,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7E9387-1550-4ADB-99E4-D27DCF0AEBD0}">
-  <dimension ref="A1:AS54"/>
+  <dimension ref="A1:AS50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" customWidth="1"/>
+    <col min="5" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="15" width="0" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="27" max="27" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="0" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="28" max="44" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -8587,35 +8605,35 @@
         <v>50</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R5" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R20" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; }; -- Conquest of Dargazag</v>
       </c>
       <c r="S3" s="1" t="str">
-        <f t="shared" ref="S3:S5" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
+        <f t="shared" ref="S3:S20" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; ["SAVE_INDEX"] = 2; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; ["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; ["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; ["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; };</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T19" si="3">ROW()-1</f>
+        <f t="shared" ref="T3:T20" si="3">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="U3" t="str">
-        <f t="shared" ref="U3:U5" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
+        <f t="shared" ref="U3:U20" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
         <v xml:space="preserve">  [2] = {</v>
       </c>
       <c r="V3" t="str">
-        <f t="shared" ref="V3:V5" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <f t="shared" ref="V3:V20" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W5" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <f t="shared" ref="W3:W20" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X5" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
+        <f t="shared" ref="X3:X20" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1" t="str">
-        <f t="shared" ref="Y3:Y5" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
+        <f t="shared" ref="Y3:Y20" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
         <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="Z3">
@@ -8623,7 +8641,7 @@
         <v>4</v>
       </c>
       <c r="AA3" t="str">
-        <f t="shared" ref="AA3:AA19" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
+        <f t="shared" ref="AA3:AA20" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
         <v xml:space="preserve">["TYPE"] =  4; </v>
       </c>
       <c r="AB3" t="str">
@@ -8631,31 +8649,31 @@
         <v/>
       </c>
       <c r="AC3" t="str">
-        <f t="shared" ref="AC3:AC5" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
+        <f t="shared" ref="AC3:AC20" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
         <v/>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD5" si="11">TEXT(F3,0)</f>
+        <f t="shared" ref="AD3:AD20" si="11">TEXT(F3,0)</f>
         <v>0</v>
       </c>
       <c r="AE3" t="str">
-        <f t="shared" ref="AE3:AE5" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
+        <f t="shared" ref="AE3:AE20" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF3" t="str">
-        <f t="shared" ref="AF3:AF5" si="13">TEXT(H3,0)</f>
+        <f t="shared" ref="AF3:AF20" si="13">TEXT(H3,0)</f>
         <v>0</v>
       </c>
       <c r="AG3" t="str">
-        <f t="shared" ref="AG3:AG5" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
+        <f t="shared" ref="AG3:AG20" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH5" si="15">TEXT(I3,0)</f>
+        <f t="shared" ref="AH3:AH20" si="15">TEXT(I3,0)</f>
         <v>0</v>
       </c>
       <c r="AI3" t="str">
-        <f t="shared" ref="AI3:AI5" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
+        <f t="shared" ref="AI3:AI20" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ3">
@@ -8663,39 +8681,39 @@
         <v>1</v>
       </c>
       <c r="AK3" t="str">
-        <f t="shared" ref="AK3:AK5" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
+        <f t="shared" ref="AK3:AK20" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL5" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
+        <f t="shared" ref="AL3:AL20" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM3" t="str">
-        <f t="shared" ref="AM3:AM5" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
+        <f t="shared" ref="AM3:AM20" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
         <v xml:space="preserve">["MIN_LVL"] = "50"; </v>
       </c>
       <c r="AN3" t="str">
-        <f t="shared" ref="AN3:AN5" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
+        <f t="shared" ref="AN3:AN20" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
         <v/>
       </c>
       <c r="AO3" t="str">
-        <f t="shared" ref="AO3:AO5" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <f t="shared" ref="AO3:AO20" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; </v>
       </c>
       <c r="AP3" t="str">
-        <f t="shared" ref="AP3:AP5" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
+        <f t="shared" ref="AP3:AP20" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; </v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ5" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <f t="shared" ref="AQ3:AQ20" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; </v>
       </c>
       <c r="AR3" t="str">
-        <f t="shared" ref="AR3:AR5" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
+        <f t="shared" ref="AR3:AR20" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; </v>
       </c>
       <c r="AS3" t="str">
-        <f t="shared" ref="AS3:AS19" si="25">CONCATENATE("};")</f>
+        <f t="shared" ref="AS3:AS20" si="25">CONCATENATE("};")</f>
         <v>};</v>
       </c>
     </row>
@@ -8976,21 +8994,21 @@
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="C6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="P6">
         <v>308</v>
       </c>
       <c r="R6" t="str">
-        <f t="shared" ref="R6:R19" si="26">CONCATENATE(U6,W6,X6,AS6," -- ",C6)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">  [5] = {["CAT_ID"] = 308; }; -- - Monster Player Reward Season 1 -</v>
       </c>
       <c r="S6" s="1" t="str">
-        <f t="shared" ref="S6:S19" si="27">CONCATENATE(U6,V6,Y6,AA6,AC6,AE6,AG6,AI6,AK6,AL6,AM6,AN6,AO6,AP6,AQ6,AR6,AS6)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">  [5] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Monster Player Reward Season 1 -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T6">
@@ -8998,23 +9016,23 @@
         <v>5</v>
       </c>
       <c r="U6" t="str">
-        <f t="shared" ref="U6:U19" si="28">CONCATENATE(REPT(" ",3-LEN(T6)),"[",T6,"] = {")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">  [5] = {</v>
       </c>
       <c r="V6" t="str">
-        <f t="shared" ref="V6:V19" si="29">IF(LEN(A6)&gt;0,CONCATENATE("[""ID""] = ",A6,"; "),"                     ")</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W6" t="str">
-        <f t="shared" ref="W6:W19" si="30">IF(LEN(A6)&gt;0,CONCATENATE("[""ID""] = ",A6,"; "),"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X6" t="str">
-        <f t="shared" ref="X6:X19" si="31">IF(LEN(P6)&gt;0,CONCATENATE("[""CAT_ID""] = ",P6,"; "),"")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">["CAT_ID"] = 308; </v>
       </c>
       <c r="Y6" s="1" t="str">
-        <f t="shared" ref="Y6:Y19" si="32">IF(LEN(B6)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B6)),B6,"; "),REPT(" ",20))</f>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z6">
@@ -9030,31 +9048,31 @@
         <v/>
       </c>
       <c r="AC6" t="str">
-        <f t="shared" ref="AC6:AC19" si="33">IF(NOT(ISBLANK(E6)),CONCATENATE("[""NA""] = ",AB6,"; "),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD6" t="str">
-        <f t="shared" ref="AD6:AD19" si="34">TEXT(F6,0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE6" t="str">
-        <f t="shared" ref="AE6:AE19" si="35">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD6)),TEXT(AD6,"0"),"; ")</f>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF6" t="str">
-        <f t="shared" ref="AF6:AF19" si="36">TEXT(H6,0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG6" t="str">
-        <f t="shared" ref="AG6:AG19" si="37">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF6)),TEXT(AF6,"0"),"; ")</f>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH6" t="str">
-        <f t="shared" ref="AH6:AH19" si="38">TEXT(I6,0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI6" t="str">
-        <f t="shared" ref="AI6:AI19" si="39">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH6)),TEXT(AH6,"0"),"; ")</f>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ6">
@@ -9062,35 +9080,35 @@
         <v>1</v>
       </c>
       <c r="AK6" t="str">
-        <f t="shared" ref="AK6:AK19" si="40">CONCATENATE("[""FACTION""] = ",TEXT(AJ6,"0"),"; ")</f>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL6" t="str">
-        <f t="shared" ref="AL6:AL19" si="41">CONCATENATE("[""TIER""] = ",TEXT(M6,"0"),"; ")</f>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM6" t="str">
-        <f t="shared" ref="AM6:AM19" si="42">IF(LEN(N6)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N6)),"""",N6,"""; "),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN6" t="str">
-        <f t="shared" ref="AN6:AN19" si="43">IF(LEN(O6)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O6)),"""",O6,"""; "),"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO6" t="str">
-        <f t="shared" ref="AO6:AO19" si="44">CONCATENATE("[""NAME""] = { [""EN""] = """,C6,"""; }; ")</f>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "- Monster Player Reward Season 1 -"; }; </v>
       </c>
       <c r="AP6" t="str">
-        <f t="shared" ref="AP6:AP19" si="45">CONCATENATE("[""LORE""] = { [""EN""] = """,L6,"""; }; ")</f>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ6" t="str">
-        <f t="shared" ref="AQ6:AQ19" si="46">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K6,"""; }; ")</f>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR6" t="str">
-        <f t="shared" ref="AR6:AR19" si="47">IF(LEN(G6)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G6,"""; }; "),"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS6" t="str">
@@ -9109,15 +9127,15 @@
         <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N7" s="2"/>
       <c r="R7" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">  [6] = {["ID"] = 1879490385; }; -- Title: Protector of Life</v>
       </c>
       <c r="S7" s="1" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">  [6] = {["ID"] = 1879490385;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Protector of Life"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T7">
@@ -9125,23 +9143,23 @@
         <v>6</v>
       </c>
       <c r="U7" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">  [6] = {</v>
       </c>
       <c r="V7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">["ID"] = 1879490385; </v>
       </c>
       <c r="W7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">["ID"] = 1879490385; </v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y7" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z7">
@@ -9157,31 +9175,31 @@
         <v>3</v>
       </c>
       <c r="AC7" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">["NA"] = 3; </v>
       </c>
       <c r="AD7" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE7" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF7" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG7" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH7" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI7" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ7">
@@ -9189,35 +9207,35 @@
         <v>1</v>
       </c>
       <c r="AK7" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL7" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM7" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN7" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO7" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Protector of Life"; }; </v>
       </c>
       <c r="AP7" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ7" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR7" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS7" t="str">
@@ -9236,15 +9254,15 @@
         <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N8" s="2"/>
       <c r="R8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">  [7] = {["ID"] = 1879490388; }; -- Title: Steward of the Ettenmoors</v>
       </c>
       <c r="S8" s="1" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">  [7] = {["ID"] = 1879490388;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Steward of the Ettenmoors"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T8">
@@ -9252,23 +9270,23 @@
         <v>7</v>
       </c>
       <c r="U8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">  [7] = {</v>
       </c>
       <c r="V8" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">["ID"] = 1879490388; </v>
       </c>
       <c r="W8" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">["ID"] = 1879490388; </v>
       </c>
       <c r="X8" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y8" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z8">
@@ -9284,31 +9302,31 @@
         <v>3</v>
       </c>
       <c r="AC8" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">["NA"] = 3; </v>
       </c>
       <c r="AD8" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE8" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF8" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG8" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH8" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI8" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ8">
@@ -9316,35 +9334,35 @@
         <v>1</v>
       </c>
       <c r="AK8" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL8" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM8" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN8" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO8" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Steward of the Ettenmoors"; }; </v>
       </c>
       <c r="AP8" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ8" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR8" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS8" t="str">
@@ -9354,7 +9372,7 @@
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1879490389</v>
+        <v>1879490390</v>
       </c>
       <c r="C9" t="s">
         <v>197</v>
@@ -9363,39 +9381,39 @@
         <v>154</v>
       </c>
       <c r="E9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N9" s="2"/>
       <c r="R9" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">  [8] = {["ID"] = 1879490389; }; -- Title: Servant of Shadow</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879490390; }; -- Title: Preserver of Order</v>
       </c>
       <c r="S9" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">  [8] = {["ID"] = 1879490389;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Servant of Shadow"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879490390;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Preserver of Order"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T9">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="U9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">  [8] = {</v>
       </c>
       <c r="V9" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490389; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879490390; </v>
       </c>
       <c r="W9" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490389; </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879490390; </v>
       </c>
       <c r="X9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y9" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z9">
@@ -9411,31 +9429,31 @@
         <v>3</v>
       </c>
       <c r="AC9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">["NA"] = 3; </v>
       </c>
       <c r="AD9" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH9" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ9">
@@ -9443,35 +9461,35 @@
         <v>1</v>
       </c>
       <c r="AK9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN9" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO9" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Servant of Shadow"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Preserver of Order"; }; </v>
       </c>
       <c r="AP9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS9" t="str">
@@ -9481,48 +9499,48 @@
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1879490390</v>
+        <v>1879490393</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
         <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N10" s="2"/>
       <c r="R10" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">  [9] = {["ID"] = 1879490390; }; -- Title: Preserver of Order</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  [9] = {["ID"] = 1879490393; }; -- Title: Exemplar</v>
       </c>
       <c r="S10" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">  [9] = {["ID"] = 1879490390;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Preserver of Order"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">  [9] = {["ID"] = 1879490393;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Exemplar"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T10">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="U10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">  [9] = {</v>
       </c>
       <c r="V10" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490390; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879490393; </v>
       </c>
       <c r="W10" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490390; </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879490393; </v>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y10" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z10">
@@ -9538,31 +9556,31 @@
         <v>3</v>
       </c>
       <c r="AC10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">["NA"] = 3; </v>
       </c>
       <c r="AD10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ10">
@@ -9570,35 +9588,35 @@
         <v>1</v>
       </c>
       <c r="AK10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO10" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Preserver of Order"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Exemplar"; }; </v>
       </c>
       <c r="AP10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS10" t="str">
@@ -9607,89 +9625,86 @@
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1879490391</v>
-      </c>
-      <c r="C11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" t="s">
-        <v>204</v>
+      <c r="C11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="N11" s="2"/>
+      <c r="P11">
+        <v>327</v>
+      </c>
       <c r="R11" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [10] = {["ID"] = 1879490391; }; -- Title: Angmar's Enforcer</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [10] = {["CAT_ID"] = 327; }; -- - Season of the Nemesis -</v>
       </c>
       <c r="S11" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve"> [10] = {["ID"] = 1879490391;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Angmar's Enforcer"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [10] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of the Nemesis -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="U11" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [10] = {</v>
       </c>
       <c r="V11" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490391; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">                     </v>
       </c>
       <c r="W11" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490391; </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="31"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">["CAT_ID"] = 327; </v>
       </c>
       <c r="Y11" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z11">
         <f>VLOOKUP(D11,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">["TYPE"] =  7; </v>
-      </c>
-      <c r="AB11">
+        <v xml:space="preserve">["TYPE"] = 14; </v>
+      </c>
+      <c r="AB11" t="str">
         <f>IF(NOT(ISBLANK(E11)),VLOOKUP(E11,[1]Type!D$2:E$6,2,FALSE),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC11" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">["NA"] = 3; </v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="AD11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG11" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH11" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI11" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ11">
@@ -9697,35 +9712,35 @@
         <v>1</v>
       </c>
       <c r="AK11" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL11" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM11" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN11" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO11" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Angmar's Enforcer"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of the Nemesis -"; }; </v>
       </c>
       <c r="AP11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR11" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS11" t="str">
@@ -9735,48 +9750,45 @@
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>1879490392</v>
+        <v>1879509060</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
         <v>154</v>
       </c>
-      <c r="E12" t="s">
-        <v>204</v>
-      </c>
       <c r="N12" s="2"/>
       <c r="R12" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [11] = {["ID"] = 1879490392; }; -- Title: Abomination</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879509060; }; -- Title: Bearer of Truth</v>
       </c>
       <c r="S12" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve"> [11] = {["ID"] = 1879490392;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Abomination"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879509060;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Bearer of Truth"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T12">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="U12" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [11] = {</v>
       </c>
       <c r="V12" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490392; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879509060; </v>
       </c>
       <c r="W12" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490392; </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879509060; </v>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y12" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z12">
@@ -9787,36 +9799,36 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
-      <c r="AB12">
+      <c r="AB12" t="str">
         <f>IF(NOT(ISBLANK(E12)),VLOOKUP(E12,[1]Type!D$2:E$6,2,FALSE),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC12" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">["NA"] = 3; </v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="AD12" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE12" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF12" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG12" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH12" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI12" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ12">
@@ -9824,35 +9836,35 @@
         <v>1</v>
       </c>
       <c r="AK12" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL12" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM12" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN12" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO12" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Abomination"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Bearer of Truth"; }; </v>
       </c>
       <c r="AP12" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ12" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR12" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS12" t="str">
@@ -9861,89 +9873,86 @@
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1879490393</v>
-      </c>
-      <c r="C13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" t="s">
-        <v>204</v>
+      <c r="C13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="N13" s="2"/>
+      <c r="P13">
+        <v>328</v>
+      </c>
       <c r="R13" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [12] = {["ID"] = 1879490393; }; -- Title: Exemplar</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [12] = {["CAT_ID"] = 328; }; -- - Season of Malice -</v>
       </c>
       <c r="S13" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve"> [12] = {["ID"] = 1879490393;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Exemplar"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [12] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Malice -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T13">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="U13" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [12] = {</v>
       </c>
       <c r="V13" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490393; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">                     </v>
       </c>
       <c r="W13" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490393; </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="31"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">["CAT_ID"] = 328; </v>
       </c>
       <c r="Y13" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z13">
         <f>VLOOKUP(D13,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">["TYPE"] =  7; </v>
-      </c>
-      <c r="AB13">
+        <v xml:space="preserve">["TYPE"] = 14; </v>
+      </c>
+      <c r="AB13" t="str">
         <f>IF(NOT(ISBLANK(E13)),VLOOKUP(E13,[1]Type!D$2:E$6,2,FALSE),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC13" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">["NA"] = 3; </v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="AD13" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE13" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF13" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG13" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ13">
@@ -9951,35 +9960,35 @@
         <v>1</v>
       </c>
       <c r="AK13" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL13" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM13" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN13" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO13" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Exemplar"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Malice -"; }; </v>
       </c>
       <c r="AP13" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ13" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR13" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS13" t="str">
@@ -9989,48 +9998,45 @@
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1879490394</v>
+        <v>1879509057</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
         <v>154</v>
       </c>
-      <c r="E14" t="s">
-        <v>204</v>
-      </c>
       <c r="N14" s="2"/>
       <c r="R14" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [13] = {["ID"] = 1879490394; }; -- Title: Scourge of the Ettenmoors</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879509057; }; -- Title: Benevolence Incarnate</v>
       </c>
       <c r="S14" s="1" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve"> [13] = {["ID"] = 1879490394;                     ["TYPE"] =  7; ["NA"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Scourge of the Ettenmoors"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879509057;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Benevolence Incarnate"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T14">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="U14" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [13] = {</v>
       </c>
       <c r="V14" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">["ID"] = 1879490394; </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879509057; </v>
       </c>
       <c r="W14" t="str">
-        <f t="shared" si="30"/>
-        <v xml:space="preserve">["ID"] = 1879490394; </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879509057; </v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y14" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z14">
@@ -10041,36 +10047,36 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
-      <c r="AB14">
+      <c r="AB14" t="str">
         <f>IF(NOT(ISBLANK(E14)),VLOOKUP(E14,[1]Type!D$2:E$6,2,FALSE),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="AC14" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">["NA"] = 3; </v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="AD14" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE14" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF14" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG14" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH14" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI14" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ14">
@@ -10078,35 +10084,35 @@
         <v>1</v>
       </c>
       <c r="AK14" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL14" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM14" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN14" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO14" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Scourge of the Ettenmoors"; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Benevolence Incarnate"; }; </v>
       </c>
       <c r="AP14" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ14" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR14" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS14" t="str">
@@ -10115,78 +10121,86 @@
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D15" s="2"/>
+      <c r="C15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="N15" s="2"/>
+      <c r="P15">
+        <v>329</v>
+      </c>
       <c r="R15" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [14] = {}; -- </v>
-      </c>
-      <c r="S15" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [14] = {["CAT_ID"] = 329; }; -- - Season of Scorn -</v>
+      </c>
+      <c r="S15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [14] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Scorn -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T15">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="U15" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [14] = {</v>
       </c>
       <c r="V15" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W15" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="31"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">["CAT_ID"] = 329; </v>
       </c>
       <c r="Y15" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z15" t="e">
+      <c r="Z15">
         <f>VLOOKUP(D15,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" t="e">
+        <v>14</v>
+      </c>
+      <c r="AA15" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB15" t="str">
         <f>IF(NOT(ISBLANK(E15)),VLOOKUP(E15,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD15" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE15" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF15" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG15" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH15" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI15" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ15">
@@ -10194,35 +10208,35 @@
         <v>1</v>
       </c>
       <c r="AK15" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL15" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM15" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN15" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO15" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Scorn -"; }; </v>
       </c>
       <c r="AP15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ15" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS15" t="str">
@@ -10231,78 +10245,86 @@
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D16" s="2"/>
+      <c r="A16">
+        <v>1879509058</v>
+      </c>
+      <c r="C16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="R16" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [15] = {}; -- </v>
-      </c>
-      <c r="S16" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [15] = {["ID"] = 1879509058; }; -- Title: The Respected Voice</v>
+      </c>
+      <c r="S16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [15] = {["ID"] = 1879509058;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: The Respected Voice"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T16">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="U16" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [15] = {</v>
       </c>
       <c r="V16" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">                     </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879509058; </v>
       </c>
       <c r="W16" t="str">
-        <f t="shared" si="30"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879509058; </v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y16" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z16" t="e">
+      <c r="Z16">
         <f>VLOOKUP(D16,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA16" t="e">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="AB16" t="str">
         <f>IF(NOT(ISBLANK(E16)),VLOOKUP(E16,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC16" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD16" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE16" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF16" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG16" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH16" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI16" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ16">
@@ -10310,35 +10332,35 @@
         <v>1</v>
       </c>
       <c r="AK16" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL16" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM16" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN16" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO16" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: The Respected Voice"; }; </v>
       </c>
       <c r="AP16" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ16" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR16" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS16" t="str">
@@ -10346,79 +10368,87 @@
         <v>};</v>
       </c>
     </row>
-    <row r="17" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D17" s="2"/>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="C17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="N17" s="2"/>
+      <c r="P17">
+        <v>330</v>
+      </c>
       <c r="R17" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [16] = {}; -- </v>
-      </c>
-      <c r="S17" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [16] = {["CAT_ID"] = 330; }; -- - Season of Spirit -</v>
+      </c>
+      <c r="S17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [16] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Spirit -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T17">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="U17" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [16] = {</v>
       </c>
       <c r="V17" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W17" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="31"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">["CAT_ID"] = 330; </v>
       </c>
       <c r="Y17" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z17" t="e">
+      <c r="Z17">
         <f>VLOOKUP(D17,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA17" t="e">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB17" t="str">
         <f>IF(NOT(ISBLANK(E17)),VLOOKUP(E17,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC17" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD17" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE17" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF17" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG17" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH17" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI17" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ17">
@@ -10426,35 +10456,35 @@
         <v>1</v>
       </c>
       <c r="AK17" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL17" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM17" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN17" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO17" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Spirit -"; }; </v>
       </c>
       <c r="AP17" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ17" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR17" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS17" t="str">
@@ -10462,79 +10492,87 @@
         <v>};</v>
       </c>
     </row>
-    <row r="18" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D18" s="2"/>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1879509059</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
+        <v>154</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="R18" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [17] = {}; -- </v>
-      </c>
-      <c r="S18" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879509059; }; -- Title: The Spirit's Guide</v>
+      </c>
+      <c r="S18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879509059;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: The Spirit's Guide"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T18">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="U18" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [17] = {</v>
       </c>
       <c r="V18" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">                     </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879509059; </v>
       </c>
       <c r="W18" t="str">
-        <f t="shared" si="30"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879509059; </v>
       </c>
       <c r="X18" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y18" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z18" t="e">
+      <c r="Z18">
         <f>VLOOKUP(D18,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA18" t="e">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="AB18" t="str">
         <f>IF(NOT(ISBLANK(E18)),VLOOKUP(E18,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC18" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD18" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE18" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF18" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG18" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH18" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI18" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ18">
@@ -10542,35 +10580,35 @@
         <v>1</v>
       </c>
       <c r="AK18" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL18" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM18" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN18" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO18" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: The Spirit's Guide"; }; </v>
       </c>
       <c r="AP18" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ18" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR18" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS18" t="str">
@@ -10578,15 +10616,15 @@
         <v>};</v>
       </c>
     </row>
-    <row r="19" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D19" s="2"/>
       <c r="N19" s="2"/>
       <c r="R19" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> [18] = {}; -- </v>
       </c>
       <c r="S19" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="T19">
@@ -10594,23 +10632,23 @@
         <v>18</v>
       </c>
       <c r="U19" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [18] = {</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W19" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y19" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z19" t="e">
@@ -10626,31 +10664,31 @@
         <v/>
       </c>
       <c r="AC19" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD19" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE19" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF19" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG19" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH19" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI19" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ19">
@@ -10658,35 +10696,35 @@
         <v>1</v>
       </c>
       <c r="AK19" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL19" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM19" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN19" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO19" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AP19" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ19" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR19" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS19" t="str">
@@ -10694,68 +10732,170 @@
         <v>};</v>
       </c>
     </row>
-    <row r="20" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="S20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="4:45" x14ac:dyDescent="0.25">
+      <c r="R20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [19] = {}; -- </v>
+      </c>
+      <c r="S20" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="U20" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> [19] = {</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Y20" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="Z20" t="e">
+        <f>VLOOKUP(D20,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA20" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB20" t="str">
+        <f>IF(NOT(ISBLANK(E20)),VLOOKUP(E20,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AE20" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF20" t="str">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH20" t="str">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI20" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ20">
+        <f>IF(NOT(ISBLANK(J20)),VLOOKUP(J20,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK20" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL20" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AM20" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AN20" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AO20" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP20" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AQ20" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AR20" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AS20" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D21" s="2"/>
       <c r="N21" s="2"/>
       <c r="S21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D22" s="2"/>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="N22" s="2"/>
       <c r="S22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D23" s="2"/>
-      <c r="N23" s="2"/>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D24" s="2"/>
-      <c r="N24" s="2"/>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="D25" s="2"/>
-      <c r="N25" s="2"/>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="4:45" x14ac:dyDescent="0.25">
-      <c r="N26" s="2"/>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" spans="4:45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
@@ -10831,25 +10971,9 @@
       <c r="S50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S51" s="1"/>
-      <c r="Y51" s="1"/>
-    </row>
-    <row r="52" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S52" s="1"/>
-      <c r="Y52" s="1"/>
-    </row>
-    <row r="53" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S53" s="1"/>
-      <c r="Y53" s="1"/>
-    </row>
-    <row r="54" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S54" s="1"/>
-      <c r="Y54" s="1"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B9">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  <conditionalFormatting sqref="B1:B8">
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="2"/>
@@ -10858,6 +10982,7 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B3A80-CB90-4BA2-B860-A8A0C987AEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46555C2D-EABC-4F92-A401-903613573BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23085" yWindow="2475" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19110" yWindow="1365" windowWidth="18600" windowHeight="14025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -1935,9 +1935,10 @@
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="11" max="11" width="45.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="29.85546875" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2088,12 +2089,12 @@
         <v>120</v>
       </c>
       <c r="R2" t="str">
-        <f>CONCATENATE(U2,W2,X2,AS2," -- ",C2)</f>
+        <f>CONCATENATE(U2,W2,X2,AL2,AS2," -- ",C2)</f>
         <v xml:space="preserve">  [1] = {["CAT_ID"] = 120; }; -- Monster-slayer</v>
       </c>
       <c r="S2" s="1" t="str">
         <f>CONCATENATE(U2,V2,Y2,AA2,AC2,AE2,AG2,AI2,AK2,AL2,AM2,AN2,AO2,AP2,AQ2,AR2,AS2)</f>
-        <v xml:space="preserve">  [1] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Monster-slayer"; }; };</v>
+        <v xml:space="preserve">  [1] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Monster-slayer"; }; };</v>
       </c>
       <c r="T2">
         <f>ROW()-1</f>
@@ -2168,8 +2169,8 @@
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL2" t="str">
-        <f>CONCATENATE("[""TIER""] = ",TEXT(M2,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f>IF(M2&gt;0,CONCATENATE("[""TIER""] = ",TEXT(M2,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AM2" t="str">
         <f>IF(LEN(N2)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N2)),"""",N2,"""; "),"                    ")</f>
@@ -2229,12 +2230,12 @@
         <v>30</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R45" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R45" si="1">CONCATENATE(U3,W3,X3,AL3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071804; }; -- Monster-slayer -- Tier 7</v>
       </c>
       <c r="S3" s="1" t="str">
         <f t="shared" ref="S3:S46" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
-        <v xml:space="preserve">  [2] = {["ID"] = 1879071804; ["SAVE_INDEX"] =  1; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Monster-slayer -- Tier 7"; }; ["LORE"] = { ["EN"] = "Stem the tides of Darkness in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 50000 monster-players in the War"; }; ["TITLE"] = { ["EN"] = "Hero of Legend"; }; };</v>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879071804; ["SAVE_INDEX"] =  1; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Monster-slayer -- Tier 7"; }; ["LORE"] = { ["EN"] = "Stem the tides of Darkness in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 50000 monster-players in the War"; }; ["TITLE"] = { ["EN"] = "Hero of Legend"; }; };</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T46" si="3">ROW()-1</f>
@@ -2309,8 +2310,8 @@
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL46" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f t="shared" ref="AL3:AL46" si="18">IF(M3&gt;0,CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AM3" t="str">
         <f t="shared" ref="AM3:AM46" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"                    ")</f>
@@ -2371,7 +2372,7 @@
       </c>
       <c r="R4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879071803; }; -- Monster-slayer -- Tier 6</v>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879071803; ["TIER"] = 1; }; -- Monster-slayer -- Tier 6</v>
       </c>
       <c r="S4" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2513,7 +2514,7 @@
       </c>
       <c r="R5" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879071802; }; -- Monster-slayer -- Tier 5</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879071802; ["TIER"] = 2; }; -- Monster-slayer -- Tier 5</v>
       </c>
       <c r="S5" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2654,7 +2655,7 @@
       </c>
       <c r="R6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879071801; }; -- Monster-slayer -- Tier 4</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879071801; ["TIER"] = 3; }; -- Monster-slayer -- Tier 4</v>
       </c>
       <c r="S6" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="R7" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879071800; }; -- Monster-slayer -- Tier 3</v>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879071800; ["TIER"] = 4; }; -- Monster-slayer -- Tier 3</v>
       </c>
       <c r="S7" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2936,7 +2937,7 @@
       </c>
       <c r="R8" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879071799; }; -- Monster-slayer -- Tier 2</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879071799; ["TIER"] = 5; }; -- Monster-slayer -- Tier 2</v>
       </c>
       <c r="S8" s="1" t="str">
         <f t="shared" si="2"/>
@@ -3077,7 +3078,7 @@
       </c>
       <c r="R9" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [8] = {["ID"] = 1879071798; }; -- Monster-slayer -- Tier 1</v>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879071798; ["TIER"] = 6; }; -- Monster-slayer -- Tier 1</v>
       </c>
       <c r="S9" s="1" t="str">
         <f t="shared" si="2"/>
@@ -3204,7 +3205,7 @@
       </c>
       <c r="S10" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [9] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Blackarrow-slayer"; }; };</v>
+        <v xml:space="preserve">  [9] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Blackarrow-slayer"; }; };</v>
       </c>
       <c r="T10">
         <f t="shared" si="3"/>
@@ -3280,7 +3281,7 @@
       </c>
       <c r="AL10" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM10" t="str">
         <f t="shared" si="19"/>
@@ -3346,7 +3347,7 @@
       </c>
       <c r="S11" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [10] = {["ID"] = 1879071809; ["SAVE_INDEX"] =  8; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Blackarrow-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Uruk-blackarrows in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Uruk-blackarrows in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Blackarrow's Executioner"; }; };</v>
+        <v xml:space="preserve"> [10] = {["ID"] = 1879071809; ["SAVE_INDEX"] =  8; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Blackarrow-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Uruk-blackarrows in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Uruk-blackarrows in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Blackarrow's Executioner"; }; };</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="AL11" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM11" t="str">
         <f t="shared" si="19"/>
@@ -3483,7 +3484,7 @@
       </c>
       <c r="R12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [11] = {["ID"] = 1879071808; }; -- Blackarrow-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879071808; ["TIER"] = 1; }; -- Blackarrow-slayer -- Tier 4</v>
       </c>
       <c r="S12" s="1" t="str">
         <f t="shared" si="2"/>
@@ -3624,7 +3625,7 @@
       </c>
       <c r="R13" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [12] = {["ID"] = 1879071807; }; -- Blackarrow-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [12] = {["ID"] = 1879071807; ["TIER"] = 2; }; -- Blackarrow-slayer -- Tier 3</v>
       </c>
       <c r="S13" s="1" t="str">
         <f t="shared" si="2"/>
@@ -3765,7 +3766,7 @@
       </c>
       <c r="R14" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [13] = {["ID"] = 1879071806; }; -- Blackarrow-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879071806; ["TIER"] = 3; }; -- Blackarrow-slayer -- Tier 2</v>
       </c>
       <c r="S14" s="1" t="str">
         <f t="shared" si="2"/>
@@ -3906,7 +3907,7 @@
       </c>
       <c r="R15" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [14] = {["ID"] = 1879071805; }; -- Blackarrow-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [14] = {["ID"] = 1879071805; ["TIER"] = 4; }; -- Blackarrow-slayer -- Tier 1</v>
       </c>
       <c r="S15" s="1" t="str">
         <f t="shared" si="2"/>
@@ -4033,7 +4034,7 @@
       </c>
       <c r="S16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [15] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Reaver-slayer"; }; };</v>
+        <v xml:space="preserve"> [15] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Reaver-slayer"; }; };</v>
       </c>
       <c r="T16">
         <f t="shared" si="3"/>
@@ -4109,7 +4110,7 @@
       </c>
       <c r="AL16" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM16" t="str">
         <f t="shared" si="19"/>
@@ -4175,7 +4176,7 @@
       </c>
       <c r="S17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [16] = {["ID"] = 1879071814; ["SAVE_INDEX"] = 13; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Reaver-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Orc-reavers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Reavers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Reaver's End"; }; };</v>
+        <v xml:space="preserve"> [16] = {["ID"] = 1879071814; ["SAVE_INDEX"] = 13; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Reaver-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Orc-reavers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Reavers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Reaver's End"; }; };</v>
       </c>
       <c r="T17">
         <f t="shared" si="3"/>
@@ -4251,7 +4252,7 @@
       </c>
       <c r="AL17" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM17" t="str">
         <f t="shared" si="19"/>
@@ -4312,7 +4313,7 @@
       </c>
       <c r="R18" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [17] = {["ID"] = 1879071813; }; -- Reaver-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879071813; ["TIER"] = 1; }; -- Reaver-slayer -- Tier 4</v>
       </c>
       <c r="S18" s="1" t="str">
         <f t="shared" si="2"/>
@@ -4453,7 +4454,7 @@
       </c>
       <c r="R19" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [18] = {["ID"] = 1879071812; }; -- Reaver-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [18] = {["ID"] = 1879071812; ["TIER"] = 2; }; -- Reaver-slayer -- Tier 3</v>
       </c>
       <c r="S19" s="1" t="str">
         <f t="shared" si="2"/>
@@ -4594,7 +4595,7 @@
       </c>
       <c r="R20" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [19] = {["ID"] = 1879071811; }; -- Reaver-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879071811; ["TIER"] = 3; }; -- Reaver-slayer -- Tier 2</v>
       </c>
       <c r="S20" s="1" t="str">
         <f t="shared" si="2"/>
@@ -4735,7 +4736,7 @@
       </c>
       <c r="R21" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [20] = {["ID"] = 1879071810; }; -- Reaver-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [20] = {["ID"] = 1879071810; ["TIER"] = 4; }; -- Reaver-slayer -- Tier 1</v>
       </c>
       <c r="S21" s="1" t="str">
         <f t="shared" si="2"/>
@@ -4862,7 +4863,7 @@
       </c>
       <c r="S22" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [21] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Defiler-slayer"; }; };</v>
+        <v xml:space="preserve"> [21] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Defiler-slayer"; }; };</v>
       </c>
       <c r="T22">
         <f t="shared" si="3"/>
@@ -4938,7 +4939,7 @@
       </c>
       <c r="AL22" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM22" t="str">
         <f t="shared" si="19"/>
@@ -5003,7 +5004,7 @@
       </c>
       <c r="S23" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [22] = {["ID"] = 1879071819; ["SAVE_INDEX"] = 18; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Defiler-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Orc-defilers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Defilers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Weird of the Defilers"; }; };</v>
+        <v xml:space="preserve"> [22] = {["ID"] = 1879071819; ["SAVE_INDEX"] = 18; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Defiler-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Orc-defilers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Defilers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Weird of the Defilers"; }; };</v>
       </c>
       <c r="T23">
         <f t="shared" si="3"/>
@@ -5079,7 +5080,7 @@
       </c>
       <c r="AL23" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM23" t="str">
         <f t="shared" si="19"/>
@@ -5140,7 +5141,7 @@
       </c>
       <c r="R24" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [23] = {["ID"] = 1879071818; }; -- Defiler-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [23] = {["ID"] = 1879071818; ["TIER"] = 1; }; -- Defiler-slayer -- Tier 4</v>
       </c>
       <c r="S24" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5281,7 +5282,7 @@
       </c>
       <c r="R25" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [24] = {["ID"] = 1879071817; }; -- Defiler-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [24] = {["ID"] = 1879071817; ["TIER"] = 2; }; -- Defiler-slayer -- Tier 3</v>
       </c>
       <c r="S25" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5423,7 +5424,7 @@
       </c>
       <c r="R26" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [25] = {["ID"] = 1879071816; }; -- Defiler-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [25] = {["ID"] = 1879071816; ["TIER"] = 3; }; -- Defiler-slayer -- Tier 2</v>
       </c>
       <c r="S26" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5564,7 +5565,7 @@
       </c>
       <c r="R27" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [26] = {["ID"] = 1879071815; }; -- Defiler-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [26] = {["ID"] = 1879071815; ["TIER"] = 4; }; -- Defiler-slayer -- Tier 1</v>
       </c>
       <c r="S27" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5691,7 +5692,7 @@
       </c>
       <c r="S28" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [27] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Stalker-slayer"; }; };</v>
+        <v xml:space="preserve"> [27] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Stalker-slayer"; }; };</v>
       </c>
       <c r="T28">
         <f t="shared" si="3"/>
@@ -5767,7 +5768,7 @@
       </c>
       <c r="AL28" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM28" t="str">
         <f t="shared" si="19"/>
@@ -5832,7 +5833,7 @@
       </c>
       <c r="S29" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [28] = {["ID"] = 1879071824; ["SAVE_INDEX"] = 23; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Stalker-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Warg-stalkers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Stalkers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Stalker's Nemesis"; }; };</v>
+        <v xml:space="preserve"> [28] = {["ID"] = 1879071824; ["SAVE_INDEX"] = 23; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Stalker-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Warg-stalkers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Stalkers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Stalker's Nemesis"; }; };</v>
       </c>
       <c r="T29">
         <f t="shared" si="3"/>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="AL29" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM29" t="str">
         <f t="shared" si="19"/>
@@ -5969,7 +5970,7 @@
       </c>
       <c r="R30" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [29] = {["ID"] = 1879071823; }; -- Stalker-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [29] = {["ID"] = 1879071823; ["TIER"] = 1; }; -- Stalker-slayer -- Tier 4</v>
       </c>
       <c r="S30" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6110,7 +6111,7 @@
       </c>
       <c r="R31" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [30] = {["ID"] = 1879071822; }; -- Stalker-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [30] = {["ID"] = 1879071822; ["TIER"] = 2; }; -- Stalker-slayer -- Tier 3</v>
       </c>
       <c r="S31" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6252,7 +6253,7 @@
       </c>
       <c r="R32" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [31] = {["ID"] = 1879071821; }; -- Stalker-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [31] = {["ID"] = 1879071821; ["TIER"] = 3; }; -- Stalker-slayer -- Tier 2</v>
       </c>
       <c r="S32" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6393,7 +6394,7 @@
       </c>
       <c r="R33" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [32] = {["ID"] = 1879071820; }; -- Stalker-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [32] = {["ID"] = 1879071820; ["TIER"] = 4; }; -- Stalker-slayer -- Tier 1</v>
       </c>
       <c r="S33" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6520,7 +6521,7 @@
       </c>
       <c r="S34" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [33] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Warleader-slayer"; }; };</v>
+        <v xml:space="preserve"> [33] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Warleader-slayer"; }; };</v>
       </c>
       <c r="T34">
         <f t="shared" si="3"/>
@@ -6596,7 +6597,7 @@
       </c>
       <c r="AL34" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM34" t="str">
         <f t="shared" si="19"/>
@@ -6661,7 +6662,7 @@
       </c>
       <c r="S35" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [34] = {["ID"] = 1879071829; ["SAVE_INDEX"] = 28; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Warleader-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Uruk-warleaders in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Warleaders in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "War-leader's Doom"; }; };</v>
+        <v xml:space="preserve"> [34] = {["ID"] = 1879071829; ["SAVE_INDEX"] = 28; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Warleader-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Uruk-warleaders in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Warleaders in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "War-leader's Doom"; }; };</v>
       </c>
       <c r="T35">
         <f t="shared" si="3"/>
@@ -6737,7 +6738,7 @@
       </c>
       <c r="AL35" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM35" t="str">
         <f t="shared" si="19"/>
@@ -6798,7 +6799,7 @@
       </c>
       <c r="R36" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [35] = {["ID"] = 1879071828; }; -- Warleader-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [35] = {["ID"] = 1879071828; ["TIER"] = 1; }; -- Warleader-slayer -- Tier 4</v>
       </c>
       <c r="S36" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6939,7 +6940,7 @@
       </c>
       <c r="R37" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [36] = {["ID"] = 1879071827; }; -- Warleader-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [36] = {["ID"] = 1879071827; ["TIER"] = 2; }; -- Warleader-slayer -- Tier 3</v>
       </c>
       <c r="S37" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7080,7 +7081,7 @@
       </c>
       <c r="R38" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [37] = {["ID"] = 1879071826; }; -- Warleader-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [37] = {["ID"] = 1879071826; ["TIER"] = 3; }; -- Warleader-slayer -- Tier 2</v>
       </c>
       <c r="S38" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7221,7 +7222,7 @@
       </c>
       <c r="R39" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [38] = {["ID"] = 1879071825; }; -- Warleader-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [38] = {["ID"] = 1879071825; ["TIER"] = 4; }; -- Warleader-slayer -- Tier 1</v>
       </c>
       <c r="S39" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7348,7 +7349,7 @@
       </c>
       <c r="S40" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [39] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0;                     ["NAME"] = { ["EN"] = "Weaver-slayer"; }; };</v>
+        <v xml:space="preserve"> [39] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Weaver-slayer"; }; };</v>
       </c>
       <c r="T40">
         <f t="shared" si="3"/>
@@ -7424,7 +7425,7 @@
       </c>
       <c r="AL40" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM40" t="str">
         <f t="shared" si="19"/>
@@ -7489,7 +7490,7 @@
       </c>
       <c r="S41" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [40] = {["ID"] = 1879071834; ["SAVE_INDEX"] = 33; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Weaver-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Weavers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Weavers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Exterminator of Weavers"; }; };</v>
+        <v xml:space="preserve"> [40] = {["ID"] = 1879071834; ["SAVE_INDEX"] = 33; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Weaver-slayer -- Tier 5"; }; ["LORE"] = { ["EN"] = "Stem the tide of Weavers in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 10000 Weavers in the Ettenmoors"; }; ["TITLE"] = { ["EN"] = "Exterminator of Weavers"; }; };</v>
       </c>
       <c r="T41">
         <f t="shared" si="3"/>
@@ -7565,7 +7566,7 @@
       </c>
       <c r="AL41" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM41" t="str">
         <f t="shared" si="19"/>
@@ -7626,7 +7627,7 @@
       </c>
       <c r="R42" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [41] = {["ID"] = 1879071833; }; -- Weaver-slayer -- Tier 4</v>
+        <v xml:space="preserve"> [41] = {["ID"] = 1879071833; ["TIER"] = 1; }; -- Weaver-slayer -- Tier 4</v>
       </c>
       <c r="S42" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7767,7 +7768,7 @@
       </c>
       <c r="R43" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [42] = {["ID"] = 1879071832; }; -- Weaver-slayer -- Tier 3</v>
+        <v xml:space="preserve"> [42] = {["ID"] = 1879071832; ["TIER"] = 2; }; -- Weaver-slayer -- Tier 3</v>
       </c>
       <c r="S43" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7908,7 +7909,7 @@
       </c>
       <c r="R44" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [43] = {["ID"] = 1879071831; }; -- Weaver-slayer -- Tier 2</v>
+        <v xml:space="preserve"> [43] = {["ID"] = 1879071831; ["TIER"] = 3; }; -- Weaver-slayer -- Tier 2</v>
       </c>
       <c r="S44" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8049,7 +8050,7 @@
       </c>
       <c r="R45" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [44] = {["ID"] = 1879071830; }; -- Weaver-slayer -- Tier 1</v>
+        <v xml:space="preserve"> [44] = {["ID"] = 1879071830; ["TIER"] = 4; }; -- Weaver-slayer -- Tier 1</v>
       </c>
       <c r="S45" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8239,7 +8240,7 @@
       </c>
       <c r="AL46" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM46" t="str">
         <f t="shared" si="19"/>
@@ -8281,6 +8282,7 @@
     <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10995,9 +10997,10 @@
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="11" max="11" width="55" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="31.42578125" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="38" max="38" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -11163,12 +11166,12 @@
         <v>90</v>
       </c>
       <c r="R2" t="str">
-        <f>CONCATENATE(U2,W2,X2,AS2," -- ",C2)</f>
+        <f>CONCATENATE(U2,W2,X2,AL2,AS2," -- ",C2)</f>
         <v xml:space="preserve">  [1] = {["ID"] = 1879326392; }; -- The Battle for Osgiliath</v>
       </c>
       <c r="S2" s="1" t="str">
         <f>CONCATENATE(U2,V2,Y2,AA2,AC2,AE2,AG2,AI2,AK2,AL2,AM2,AN2,AO2,AP2,AQ2,AR2,AS2)</f>
-        <v xml:space="preserve">  [1] = {["ID"] = 1879326392; ["SAVE_INDEX"] = 1; ["TYPE"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "90"; ["NAME"] = { ["EN"] = "The Battle for Osgiliath"; }; ["LORE"] = { ["EN"] = "Explore the battleground of Osgiliath."; }; ["SUMMARY"] = { ["EN"] = "Discover 7 locations"; }; ["TITLE"] = { ["EN"] = "Surveyor of Battle"; }; };</v>
+        <v xml:space="preserve">  [1] = {["ID"] = 1879326392; ["SAVE_INDEX"] = 1; ["TYPE"] = 3; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "90"; ["NAME"] = { ["EN"] = "The Battle for Osgiliath"; }; ["LORE"] = { ["EN"] = "Explore the battleground of Osgiliath."; }; ["SUMMARY"] = { ["EN"] = "Discover 7 locations"; }; ["TITLE"] = { ["EN"] = "Surveyor of Battle"; }; };</v>
       </c>
       <c r="T2">
         <f>ROW()-1</f>
@@ -11243,8 +11246,8 @@
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL2" t="str">
-        <f>CONCATENATE("[""TIER""] = ",TEXT(M2,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f>IF(M2&gt;0,CONCATENATE("[""TIER""] = ",TEXT(M2,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AM2" t="str">
         <f>IF(LEN(N2)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N2)),"""",N2,"""; "),"")</f>
@@ -11301,12 +11304,12 @@
         <v>50</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R9" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R9" si="1">CONCATENATE(U3,W3,X3,AL3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879326399; }; -- Quest of the Court of Anárion -- Tier 3</v>
       </c>
       <c r="S3" s="1" t="str">
         <f t="shared" ref="S3:S9" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
-        <v xml:space="preserve">  [2] = {["ID"] = 1879326399; ["SAVE_INDEX"] = 4; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; };</v>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879326399; ["SAVE_INDEX"] = 4; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 50 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Warrior"; }; };</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T9" si="3">ROW()-1</f>
@@ -11381,8 +11384,8 @@
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL9" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f t="shared" ref="AL3:AL9" si="18">IF(M3&gt;0,CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AM3" t="str">
         <f t="shared" ref="AM3:AM9" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
@@ -11435,16 +11438,19 @@
       <c r="L4" t="s">
         <v>151</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879326396; }; -- Quest of the Court of Anárion -- Tier 2</v>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879326396; ["TIER"] = 1; }; -- Quest of the Court of Anárion -- Tier 2</v>
       </c>
       <c r="S4" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879326396; ["SAVE_INDEX"] = 3; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 2"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 25 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Soldier"; }; };</v>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879326396; ["SAVE_INDEX"] = 3; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 1; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 2"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 25 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Soldier"; }; };</v>
       </c>
       <c r="T4">
         <f t="shared" si="3"/>
@@ -11520,7 +11526,7 @@
       </c>
       <c r="AL4" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AM4" t="str">
         <f t="shared" si="19"/>
@@ -11573,16 +11579,19 @@
       <c r="L5" t="s">
         <v>151</v>
       </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
       <c r="N5">
         <v>50</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; }; -- Quest of the Court of Anárion -- Tier 1</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; ["TIER"] = 2; }; -- Quest of the Court of Anárion -- Tier 1</v>
       </c>
       <c r="S5" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; ["SAVE_INDEX"] = 2; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; };</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879326410; ["SAVE_INDEX"] = 2; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 2; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Court of Anárion -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captain of the Court of Anárion will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 10 quests for the benefit of the Court of Anárion!"; }; ["TITLE"] = { ["EN"] = "Gondorian Recruit"; }; };</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
@@ -11658,7 +11667,7 @@
       </c>
       <c r="AL5" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 2; </v>
       </c>
       <c r="AM5" t="str">
         <f t="shared" si="19"/>
@@ -11720,7 +11729,7 @@
       </c>
       <c r="S6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879326398; ["SAVE_INDEX"] = 7; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; };</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879326398; ["SAVE_INDEX"] = 7; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 3"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 80 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Shield of Eldacar"; }; };</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
@@ -11796,7 +11805,7 @@
       </c>
       <c r="AL6" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM6" t="str">
         <f t="shared" si="19"/>
@@ -11849,16 +11858,19 @@
       <c r="L7" t="s">
         <v>159</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
       <c r="N7">
         <v>50</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879326401; }; -- Quest of the Palace of Eldacar -- Tier 2</v>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879326401; ["TIER"] = 1; }; -- Quest of the Palace of Eldacar -- Tier 2</v>
       </c>
       <c r="S7" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879326401; ["SAVE_INDEX"] = 6; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 2"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 40 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Protector of Eldacar"; }; };</v>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879326401; ["SAVE_INDEX"] = 6; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 1; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 2"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 40 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Protector of Eldacar"; }; };</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
@@ -11934,7 +11946,7 @@
       </c>
       <c r="AL7" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AM7" t="str">
         <f t="shared" si="19"/>
@@ -11987,16 +11999,19 @@
       <c r="L8" t="s">
         <v>159</v>
       </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
       <c r="N8">
         <v>50</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; }; -- Quest of the Palace of Eldacar -- Tier 1</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; ["TIER"] = 2; }; -- Quest of the Palace of Eldacar -- Tier 1</v>
       </c>
       <c r="S8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; ["SAVE_INDEX"] = 5; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; };</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879326404; ["SAVE_INDEX"] = 5; ["TYPE"] = 7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 2; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Quest of the Palace of Eldacar -- Tier 1"; }; ["LORE"] = { ["EN"] = "Service to the captains of the Palace of Eldacar will result in the ability to find your way through the city with less effort."; }; ["SUMMARY"] = { ["EN"] = "Complete 15 quests for the benefit of the Palace of Eldacar!"; }; ["TITLE"] = { ["EN"] = "Defender of Eldacar"; }; };</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
@@ -12072,7 +12087,7 @@
       </c>
       <c r="AL8" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 2; </v>
       </c>
       <c r="AM8" t="str">
         <f t="shared" si="19"/>
@@ -12186,7 +12201,7 @@
       </c>
       <c r="AL9" t="str">
         <f t="shared" si="18"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AM9" t="str">
         <f t="shared" si="19"/>
@@ -12411,6 +12426,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46555C2D-EABC-4F92-A401-903613573BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689AA7FF-03F4-4D57-96A6-0FA5B8F044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19110" yWindow="1365" windowWidth="18600" windowHeight="14025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="211">
   <si>
     <t>Save Index</t>
   </si>
@@ -666,6 +666,12 @@
   </si>
   <si>
     <t>Title: Bearer of Truth</t>
+  </si>
+  <si>
+    <t>Title: Bastion of Light</t>
+  </si>
+  <si>
+    <t>- Monster Player Reward Season 6 -</t>
   </si>
 </sst>
 </file>
@@ -858,6 +864,7 @@
       <sheetName val="Return to Carn Dûm"/>
       <sheetName val="Corsairs of Umbar"/>
       <sheetName val="The Legacy of Morgoth"/>
+      <sheetName val="Kingdoms of Harad"/>
       <sheetName val="&lt;template&gt;"/>
     </sheetNames>
     <sheetDataSet>
@@ -1660,6 +1667,7 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8288,7 +8296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7E9387-1550-4ADB-99E4-D27DCF0AEBD0}">
-  <dimension ref="A1:AS50"/>
+  <dimension ref="A1:AS52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -8607,35 +8615,35 @@
         <v>50</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R20" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R22" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; }; -- Conquest of Dargazag</v>
       </c>
       <c r="S3" s="1" t="str">
-        <f t="shared" ref="S3:S20" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
+        <f t="shared" ref="S3:S22" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; ["SAVE_INDEX"] = 2; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; ["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; ["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; ["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; };</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T20" si="3">ROW()-1</f>
+        <f t="shared" ref="T3:T22" si="3">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="U3" t="str">
-        <f t="shared" ref="U3:U20" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
+        <f t="shared" ref="U3:U22" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
         <v xml:space="preserve">  [2] = {</v>
       </c>
       <c r="V3" t="str">
-        <f t="shared" ref="V3:V20" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <f t="shared" ref="V3:V22" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W20" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <f t="shared" ref="W3:W22" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X20" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
+        <f t="shared" ref="X3:X22" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1" t="str">
-        <f t="shared" ref="Y3:Y20" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
+        <f t="shared" ref="Y3:Y22" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
         <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="Z3">
@@ -8643,7 +8651,7 @@
         <v>4</v>
       </c>
       <c r="AA3" t="str">
-        <f t="shared" ref="AA3:AA20" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
+        <f t="shared" ref="AA3:AA22" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
         <v xml:space="preserve">["TYPE"] =  4; </v>
       </c>
       <c r="AB3" t="str">
@@ -8651,31 +8659,31 @@
         <v/>
       </c>
       <c r="AC3" t="str">
-        <f t="shared" ref="AC3:AC20" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
+        <f t="shared" ref="AC3:AC22" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
         <v/>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD20" si="11">TEXT(F3,0)</f>
+        <f t="shared" ref="AD3:AD22" si="11">TEXT(F3,0)</f>
         <v>0</v>
       </c>
       <c r="AE3" t="str">
-        <f t="shared" ref="AE3:AE20" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
+        <f t="shared" ref="AE3:AE22" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF3" t="str">
-        <f t="shared" ref="AF3:AF20" si="13">TEXT(H3,0)</f>
+        <f t="shared" ref="AF3:AF22" si="13">TEXT(H3,0)</f>
         <v>0</v>
       </c>
       <c r="AG3" t="str">
-        <f t="shared" ref="AG3:AG20" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
+        <f t="shared" ref="AG3:AG22" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH20" si="15">TEXT(I3,0)</f>
+        <f t="shared" ref="AH3:AH22" si="15">TEXT(I3,0)</f>
         <v>0</v>
       </c>
       <c r="AI3" t="str">
-        <f t="shared" ref="AI3:AI20" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
+        <f t="shared" ref="AI3:AI22" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ3">
@@ -8683,39 +8691,39 @@
         <v>1</v>
       </c>
       <c r="AK3" t="str">
-        <f t="shared" ref="AK3:AK20" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
+        <f t="shared" ref="AK3:AK22" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL20" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
+        <f t="shared" ref="AL3:AL22" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM3" t="str">
-        <f t="shared" ref="AM3:AM20" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
+        <f t="shared" ref="AM3:AM22" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
         <v xml:space="preserve">["MIN_LVL"] = "50"; </v>
       </c>
       <c r="AN3" t="str">
-        <f t="shared" ref="AN3:AN20" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
+        <f t="shared" ref="AN3:AN22" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
         <v/>
       </c>
       <c r="AO3" t="str">
-        <f t="shared" ref="AO3:AO20" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <f t="shared" ref="AO3:AO22" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; </v>
       </c>
       <c r="AP3" t="str">
-        <f t="shared" ref="AP3:AP20" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
+        <f t="shared" ref="AP3:AP22" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; </v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ20" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <f t="shared" ref="AQ3:AQ22" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; </v>
       </c>
       <c r="AR3" t="str">
-        <f t="shared" ref="AR3:AR20" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
+        <f t="shared" ref="AR3:AR22" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; </v>
       </c>
       <c r="AS3" t="str">
-        <f t="shared" ref="AS3:AS20" si="25">CONCATENATE("};")</f>
+        <f t="shared" ref="AS3:AS22" si="25">CONCATENATE("};")</f>
         <v>};</v>
       </c>
     </row>
@@ -10619,78 +10627,86 @@
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D19" s="2"/>
+      <c r="C19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="N19" s="2"/>
+      <c r="P19">
+        <v>342</v>
+      </c>
       <c r="R19" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> [18] = {}; -- </v>
-      </c>
-      <c r="S19" s="1" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
+        <f t="shared" ref="R19:R22" si="26">CONCATENATE(U19,W19,X19,AS19," -- ",C19)</f>
+        <v xml:space="preserve"> [18] = {["CAT_ID"] = 342; }; -- - Monster Player Reward Season 6 -</v>
+      </c>
+      <c r="S19" s="1" t="str">
+        <f t="shared" ref="S19:S22" si="27">CONCATENATE(U19,V19,Y19,AA19,AC19,AE19,AG19,AI19,AK19,AL19,AM19,AN19,AO19,AP19,AQ19,AR19,AS19)</f>
+        <v xml:space="preserve"> [18] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Monster Player Reward Season 6 -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T19">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="U19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="U19:U22" si="28">CONCATENATE(REPT(" ",3-LEN(T19)),"[",T19,"] = {")</f>
         <v xml:space="preserve"> [18] = {</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="V19:V22" si="29">IF(LEN(A19)&gt;0,CONCATENATE("[""ID""] = ",A19,"; "),"                     ")</f>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W19" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="W19:W22" si="30">IF(LEN(A19)&gt;0,CONCATENATE("[""ID""] = ",A19,"; "),"")</f>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" ref="X19:X22" si="31">IF(LEN(P19)&gt;0,CONCATENATE("[""CAT_ID""] = ",P19,"; "),"")</f>
+        <v xml:space="preserve">["CAT_ID"] = 342; </v>
       </c>
       <c r="Y19" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="Y19:Y22" si="32">IF(LEN(B19)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B19)),B19,"; "),REPT(" ",20))</f>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z19" t="e">
+      <c r="Z19">
         <f>VLOOKUP(D19,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA19" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>14</v>
+      </c>
+      <c r="AA19" t="str">
+        <f t="shared" ref="AA19:AA22" si="33">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z19)),Z19,"; ")</f>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB19" t="str">
         <f>IF(NOT(ISBLANK(E19)),VLOOKUP(E19,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC19" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="AC19:AC22" si="34">IF(NOT(ISBLANK(E19)),CONCATENATE("[""NA""] = ",AB19,"; "),"")</f>
         <v/>
       </c>
       <c r="AD19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AD19:AD22" si="35">TEXT(F19,0)</f>
         <v>0</v>
       </c>
       <c r="AE19" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="AE19:AE22" si="36">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD19)),TEXT(AD19,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF19" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="AF19:AF22" si="37">TEXT(H19,0)</f>
         <v>0</v>
       </c>
       <c r="AG19" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="AG19:AG22" si="38">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF19)),TEXT(AF19,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH19" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="AH19:AH22" si="39">TEXT(I19,0)</f>
         <v>0</v>
       </c>
       <c r="AI19" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AI19:AI22" si="40">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH19)),TEXT(AH19,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ19">
@@ -10698,35 +10714,35 @@
         <v>1</v>
       </c>
       <c r="AK19" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="AK19:AK22" si="41">CONCATENATE("[""FACTION""] = ",TEXT(AJ19,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL19" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="AL19:AL22" si="42">CONCATENATE("[""TIER""] = ",TEXT(M19,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="AM19:AM22" si="43">IF(LEN(N19)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N19)),"""",N19,"""; "),"")</f>
         <v/>
       </c>
       <c r="AN19" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="AN19:AN22" si="44">IF(LEN(O19)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O19)),"""",O19,"""; "),"")</f>
         <v/>
       </c>
       <c r="AO19" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" ref="AO19:AO22" si="45">CONCATENATE("[""NAME""] = { [""EN""] = """,C19,"""; }; ")</f>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Monster Player Reward Season 6 -"; }; </v>
       </c>
       <c r="AP19" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="AP19:AP22" si="46">CONCATENATE("[""LORE""] = { [""EN""] = """,L19,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ19" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="AQ19:AQ22" si="47">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K19,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR19" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="AR19:AR22" si="48">IF(LEN(G19)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G19,"""; }; "),"")</f>
         <v/>
       </c>
       <c r="AS19" t="str">
@@ -10735,78 +10751,86 @@
       </c>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D20" s="2"/>
+      <c r="A20">
+        <v>1879523597</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>154</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="R20" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> [19] = {}; -- </v>
-      </c>
-      <c r="S20" s="1" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
+        <f t="shared" si="26"/>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879523597; }; -- Title: Bastion of Light</v>
+      </c>
+      <c r="S20" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879523597;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Bastion of Light"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T20">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="U20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v xml:space="preserve"> [19] = {</v>
       </c>
       <c r="V20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">                     </v>
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">["ID"] = 1879523597; </v>
       </c>
       <c r="W20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">["ID"] = 1879523597; </v>
       </c>
       <c r="X20" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Y20" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z20" t="e">
+      <c r="Z20">
         <f>VLOOKUP(D20,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA20" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>7</v>
+      </c>
+      <c r="AA20" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="AB20" t="str">
         <f>IF(NOT(ISBLANK(E20)),VLOOKUP(E20,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC20" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD20" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AE20" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="36"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG20" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH20" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AI20" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="40"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ20">
@@ -10814,35 +10838,35 @@
         <v>1</v>
       </c>
       <c r="AK20" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL20" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM20" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AN20" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AO20" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Bastion of Light"; }; </v>
       </c>
       <c r="AP20" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ20" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR20" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AS20" t="str">
@@ -10853,19 +10877,243 @@
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="S21" s="1"/>
-      <c r="Y21" s="1"/>
+      <c r="R21" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve"> [20] = {}; -- </v>
+      </c>
+      <c r="S21" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="U21" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve"> [20] = {</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W21" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="Y21" s="1" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="Z21" t="e">
+        <f>VLOOKUP(D21,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA21" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB21" t="str">
+        <f>IF(NOT(ISBLANK(E21)),VLOOKUP(E21,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD21" t="str">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AE21" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF21" t="str">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AG21" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH21" t="str">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AI21" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ21">
+        <f>IF(NOT(ISBLANK(J21)),VLOOKUP(J21,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK21" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL21" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AM21" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN21" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO21" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP21" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AQ21" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AR21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="AS21" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="S22" s="1"/>
-      <c r="Y22" s="1"/>
+      <c r="R22" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve"> [21] = {}; -- </v>
+      </c>
+      <c r="S22" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U22" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve"> [21] = {</v>
+      </c>
+      <c r="V22" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="Y22" s="1" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="Z22" t="e">
+        <f>VLOOKUP(D22,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA22" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB22" t="str">
+        <f>IF(NOT(ISBLANK(E22)),VLOOKUP(E22,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF22" t="str">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH22" t="str">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ22">
+        <f>IF(NOT(ISBLANK(J22)),VLOOKUP(J22,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK22" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL22" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AM22" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN22" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO22" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP22" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AQ22" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AR22" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="AS22" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D23" s="2"/>
+      <c r="N23" s="2"/>
       <c r="S23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="N24" s="2"/>
       <c r="S24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
@@ -10972,6 +11220,14 @@
     <row r="50" spans="19:25" x14ac:dyDescent="0.25">
       <c r="S50" s="1"/>
       <c r="Y50" s="1"/>
+    </row>
+    <row r="51" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S51" s="1"/>
+      <c r="Y51" s="1"/>
+    </row>
+    <row r="52" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S52" s="1"/>
+      <c r="Y52" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B8">

--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689AA7FF-03F4-4D57-96A6-0FA5B8F044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD345887-F509-4311-A102-B64DB99E36BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8205" yWindow="5415" windowWidth="20895" windowHeight="10320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -635,33 +635,18 @@
     <t>Title: Preserver of Order</t>
   </si>
   <si>
-    <t>- Monster Player Reward Season 1 -</t>
-  </si>
-  <si>
     <t>Title: Exemplar</t>
   </si>
   <si>
     <t>Limited Time Only</t>
   </si>
   <si>
-    <t>- Season of the Nemesis -</t>
-  </si>
-  <si>
     <t>Title: Benevolence Incarnate</t>
   </si>
   <si>
     <t>Title: The Respected Voice</t>
   </si>
   <si>
-    <t>- Season of Scorn -</t>
-  </si>
-  <si>
-    <t>- Season of Spirit -</t>
-  </si>
-  <si>
-    <t>- Season of Malice -</t>
-  </si>
-  <si>
     <t>Title: The Spirit's Guide</t>
   </si>
   <si>
@@ -671,7 +656,22 @@
     <t>Title: Bastion of Light</t>
   </si>
   <si>
-    <t>- Monster Player Reward Season 6 -</t>
+    <t>- Season 1: Strife -</t>
+  </si>
+  <si>
+    <t>- Season 2: Nemesis -</t>
+  </si>
+  <si>
+    <t>- Season 3: Malice -</t>
+  </si>
+  <si>
+    <t>- Season 4: Scorn -</t>
+  </si>
+  <si>
+    <t>- Season 5: Spirits -</t>
+  </si>
+  <si>
+    <t>- Season 6: Rivals -</t>
   </si>
 </sst>
 </file>
@@ -721,11 +721,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -8615,11 +8614,11 @@
         <v>50</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R22" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R18" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; }; -- Conquest of Dargazag</v>
       </c>
       <c r="S3" s="1" t="str">
-        <f t="shared" ref="S3:S22" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
+        <f t="shared" ref="S3:S18" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; ["SAVE_INDEX"] = 2; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; ["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; ["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; ["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; };</v>
       </c>
       <c r="T3">
@@ -8627,23 +8626,23 @@
         <v>2</v>
       </c>
       <c r="U3" t="str">
-        <f t="shared" ref="U3:U22" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
+        <f t="shared" ref="U3:U18" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
         <v xml:space="preserve">  [2] = {</v>
       </c>
       <c r="V3" t="str">
-        <f t="shared" ref="V3:V22" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <f t="shared" ref="V3:V18" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W22" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <f t="shared" ref="W3:W18" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X22" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
+        <f t="shared" ref="X3:X18" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1" t="str">
-        <f t="shared" ref="Y3:Y22" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
+        <f t="shared" ref="Y3:Y18" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
         <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="Z3">
@@ -8651,7 +8650,7 @@
         <v>4</v>
       </c>
       <c r="AA3" t="str">
-        <f t="shared" ref="AA3:AA22" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
+        <f t="shared" ref="AA3:AA18" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
         <v xml:space="preserve">["TYPE"] =  4; </v>
       </c>
       <c r="AB3" t="str">
@@ -8659,31 +8658,31 @@
         <v/>
       </c>
       <c r="AC3" t="str">
-        <f t="shared" ref="AC3:AC22" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
+        <f t="shared" ref="AC3:AC18" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
         <v/>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD22" si="11">TEXT(F3,0)</f>
+        <f t="shared" ref="AD3:AD18" si="11">TEXT(F3,0)</f>
         <v>0</v>
       </c>
       <c r="AE3" t="str">
-        <f t="shared" ref="AE3:AE22" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
+        <f t="shared" ref="AE3:AE18" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF3" t="str">
-        <f t="shared" ref="AF3:AF22" si="13">TEXT(H3,0)</f>
+        <f t="shared" ref="AF3:AF18" si="13">TEXT(H3,0)</f>
         <v>0</v>
       </c>
       <c r="AG3" t="str">
-        <f t="shared" ref="AG3:AG22" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
+        <f t="shared" ref="AG3:AG18" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH22" si="15">TEXT(I3,0)</f>
+        <f t="shared" ref="AH3:AH18" si="15">TEXT(I3,0)</f>
         <v>0</v>
       </c>
       <c r="AI3" t="str">
-        <f t="shared" ref="AI3:AI22" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
+        <f t="shared" ref="AI3:AI18" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ3">
@@ -8691,35 +8690,35 @@
         <v>1</v>
       </c>
       <c r="AK3" t="str">
-        <f t="shared" ref="AK3:AK22" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
+        <f t="shared" ref="AK3:AK18" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL22" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
+        <f t="shared" ref="AL3:AL18" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM3" t="str">
-        <f t="shared" ref="AM3:AM22" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
+        <f t="shared" ref="AM3:AM18" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
         <v xml:space="preserve">["MIN_LVL"] = "50"; </v>
       </c>
       <c r="AN3" t="str">
-        <f t="shared" ref="AN3:AN22" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
+        <f t="shared" ref="AN3:AN18" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
         <v/>
       </c>
       <c r="AO3" t="str">
-        <f t="shared" ref="AO3:AO22" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <f t="shared" ref="AO3:AO18" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; </v>
       </c>
       <c r="AP3" t="str">
-        <f t="shared" ref="AP3:AP22" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
+        <f t="shared" ref="AP3:AP18" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; </v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ22" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <f t="shared" ref="AQ3:AQ18" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; </v>
       </c>
       <c r="AR3" t="str">
-        <f t="shared" ref="AR3:AR22" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
+        <f t="shared" ref="AR3:AR18" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; </v>
       </c>
       <c r="AS3" t="str">
@@ -9004,8 +9003,8 @@
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="C6" s="4" t="s">
-        <v>198</v>
+      <c r="C6" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>29</v>
@@ -9015,11 +9014,11 @@
       </c>
       <c r="R6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [5] = {["CAT_ID"] = 308; }; -- - Monster Player Reward Season 1 -</v>
+        <v xml:space="preserve">  [5] = {["CAT_ID"] = 308; }; -- - Season 1: Strife -</v>
       </c>
       <c r="S6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">  [5] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Monster Player Reward Season 1 -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve">  [5] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 1: Strife -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
@@ -9107,7 +9106,7 @@
       </c>
       <c r="AO6" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Monster Player Reward Season 1 -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 1: Strife -"; }; </v>
       </c>
       <c r="AP6" t="str">
         <f t="shared" si="22"/>
@@ -9137,7 +9136,7 @@
         <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N7" s="2"/>
       <c r="R7" t="str">
@@ -9264,7 +9263,7 @@
         <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N8" s="2"/>
       <c r="R8" t="str">
@@ -9391,7 +9390,7 @@
         <v>154</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N9" s="2"/>
       <c r="R9" t="str">
@@ -9512,13 +9511,13 @@
         <v>1879490393</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
         <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N10" s="2"/>
       <c r="R10" t="str">
@@ -9636,7 +9635,7 @@
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C11" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>29</v>
@@ -9647,11 +9646,11 @@
       </c>
       <c r="R11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [10] = {["CAT_ID"] = 327; }; -- - Season of the Nemesis -</v>
+        <v xml:space="preserve"> [10] = {["CAT_ID"] = 327; }; -- - Season 2: Nemesis -</v>
       </c>
       <c r="S11" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [10] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of the Nemesis -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve"> [10] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 2: Nemesis -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
@@ -9739,7 +9738,7 @@
       </c>
       <c r="AO11" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of the Nemesis -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 2: Nemesis -"; }; </v>
       </c>
       <c r="AP11" t="str">
         <f t="shared" si="22"/>
@@ -9763,7 +9762,7 @@
         <v>1879509060</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D12" t="s">
         <v>154</v>
@@ -9884,7 +9883,7 @@
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C13" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>29</v>
@@ -9895,11 +9894,11 @@
       </c>
       <c r="R13" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [12] = {["CAT_ID"] = 328; }; -- - Season of Malice -</v>
+        <v xml:space="preserve"> [12] = {["CAT_ID"] = 328; }; -- - Season 3: Malice -</v>
       </c>
       <c r="S13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [12] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Malice -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve"> [12] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 3: Malice -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T13">
         <f t="shared" si="3"/>
@@ -9987,7 +9986,7 @@
       </c>
       <c r="AO13" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Malice -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 3: Malice -"; }; </v>
       </c>
       <c r="AP13" t="str">
         <f t="shared" si="22"/>
@@ -10011,7 +10010,7 @@
         <v>1879509057</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
         <v>154</v>
@@ -10132,7 +10131,7 @@
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C15" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>29</v>
@@ -10143,11 +10142,11 @@
       </c>
       <c r="R15" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [14] = {["CAT_ID"] = 329; }; -- - Season of Scorn -</v>
+        <v xml:space="preserve"> [14] = {["CAT_ID"] = 329; }; -- - Season 4: Scorn -</v>
       </c>
       <c r="S15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [14] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Scorn -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve"> [14] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 4: Scorn -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T15">
         <f t="shared" si="3"/>
@@ -10235,7 +10234,7 @@
       </c>
       <c r="AO15" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Scorn -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 4: Scorn -"; }; </v>
       </c>
       <c r="AP15" t="str">
         <f t="shared" si="22"/>
@@ -10259,7 +10258,7 @@
         <v>1879509058</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
         <v>154</v>
@@ -10380,7 +10379,7 @@
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>29</v>
@@ -10391,11 +10390,11 @@
       </c>
       <c r="R17" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> [16] = {["CAT_ID"] = 330; }; -- - Season of Spirit -</v>
+        <v xml:space="preserve"> [16] = {["CAT_ID"] = 330; }; -- - Season 5: Spirits -</v>
       </c>
       <c r="S17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> [16] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season of Spirit -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve"> [16] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 5: Spirits -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T17">
         <f t="shared" si="3"/>
@@ -10483,7 +10482,7 @@
       </c>
       <c r="AO17" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season of Spirit -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 5: Spirits -"; }; </v>
       </c>
       <c r="AP17" t="str">
         <f t="shared" si="22"/>
@@ -10507,7 +10506,7 @@
         <v>1879509059</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
         <v>154</v>
@@ -10639,11 +10638,11 @@
       </c>
       <c r="R19" t="str">
         <f t="shared" ref="R19:R22" si="26">CONCATENATE(U19,W19,X19,AS19," -- ",C19)</f>
-        <v xml:space="preserve"> [18] = {["CAT_ID"] = 342; }; -- - Monster Player Reward Season 6 -</v>
+        <v xml:space="preserve"> [18] = {["CAT_ID"] = 342; }; -- - Season 6: Rivals -</v>
       </c>
       <c r="S19" s="1" t="str">
         <f t="shared" ref="S19:S22" si="27">CONCATENATE(U19,V19,Y19,AA19,AC19,AE19,AG19,AI19,AK19,AL19,AM19,AN19,AO19,AP19,AQ19,AR19,AS19)</f>
-        <v xml:space="preserve"> [18] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Monster Player Reward Season 6 -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
+        <v xml:space="preserve"> [18] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 6: Rivals -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T19">
         <f t="shared" si="3"/>
@@ -10731,7 +10730,7 @@
       </c>
       <c r="AO19" t="str">
         <f t="shared" ref="AO19:AO22" si="45">CONCATENATE("[""NAME""] = { [""EN""] = """,C19,"""; }; ")</f>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Monster Player Reward Season 6 -"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 6: Rivals -"; }; </v>
       </c>
       <c r="AP19" t="str">
         <f t="shared" ref="AP19:AP22" si="46">CONCATENATE("[""LORE""] = { [""EN""] = """,L19,"""; }; ")</f>
@@ -10755,7 +10754,7 @@
         <v>1879523597</v>
       </c>
       <c r="C20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
         <v>154</v>

--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD345887-F509-4311-A102-B64DB99E36BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02611CA2-B28A-4C02-A02B-361F40D261F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8205" yWindow="5415" windowWidth="20895" windowHeight="10320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="480" windowWidth="17295" windowHeight="14430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="213">
   <si>
     <t>Save Index</t>
   </si>
@@ -672,6 +672,12 @@
   </si>
   <si>
     <t>- Season 6: Rivals -</t>
+  </si>
+  <si>
+    <t>Frame: Season of Destruction Frame</t>
+  </si>
+  <si>
+    <t>- Season 7: Destruction -</t>
   </si>
 </sst>
 </file>
@@ -8614,35 +8620,35 @@
         <v>50</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R18" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R24" si="1">CONCATENATE(U3,W3,X3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; }; -- Conquest of Dargazag</v>
       </c>
       <c r="S3" s="1" t="str">
-        <f t="shared" ref="S3:S18" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
+        <f t="shared" ref="S3:S24" si="2">CONCATENATE(U3,V3,Y3,AA3,AC3,AE3,AG3,AI3,AK3,AL3,AM3,AN3,AO3,AP3,AQ3,AR3,AS3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071836; ["SAVE_INDEX"] = 2; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["MIN_LVL"] = "50"; ["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; ["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; ["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; ["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; };</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T22" si="3">ROW()-1</f>
+        <f t="shared" ref="T3:T24" si="3">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="U3" t="str">
-        <f t="shared" ref="U3:U18" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
+        <f t="shared" ref="U3:U24" si="4">CONCATENATE(REPT(" ",3-LEN(T3)),"[",T3,"] = {")</f>
         <v xml:space="preserve">  [2] = {</v>
       </c>
       <c r="V3" t="str">
-        <f t="shared" ref="V3:V18" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <f t="shared" ref="V3:V24" si="5">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W18" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <f t="shared" ref="W3:W24" si="6">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879071836; </v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X18" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
+        <f t="shared" ref="X3:X24" si="7">IF(LEN(P3)&gt;0,CONCATENATE("[""CAT_ID""] = ",P3,"; "),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1" t="str">
-        <f t="shared" ref="Y3:Y18" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
+        <f t="shared" ref="Y3:Y24" si="8">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),REPT(" ",20))</f>
         <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="Z3">
@@ -8650,7 +8656,7 @@
         <v>4</v>
       </c>
       <c r="AA3" t="str">
-        <f t="shared" ref="AA3:AA18" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
+        <f t="shared" ref="AA3:AA24" si="9">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z3)),Z3,"; ")</f>
         <v xml:space="preserve">["TYPE"] =  4; </v>
       </c>
       <c r="AB3" t="str">
@@ -8658,31 +8664,31 @@
         <v/>
       </c>
       <c r="AC3" t="str">
-        <f t="shared" ref="AC3:AC18" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
+        <f t="shared" ref="AC3:AC24" si="10">IF(NOT(ISBLANK(E3)),CONCATENATE("[""NA""] = ",AB3,"; "),"")</f>
         <v/>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD18" si="11">TEXT(F3,0)</f>
+        <f t="shared" ref="AD3:AD24" si="11">TEXT(F3,0)</f>
         <v>0</v>
       </c>
       <c r="AE3" t="str">
-        <f t="shared" ref="AE3:AE18" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
+        <f t="shared" ref="AE3:AE24" si="12">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD3)),TEXT(AD3,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF3" t="str">
-        <f t="shared" ref="AF3:AF18" si="13">TEXT(H3,0)</f>
+        <f t="shared" ref="AF3:AF24" si="13">TEXT(H3,0)</f>
         <v>0</v>
       </c>
       <c r="AG3" t="str">
-        <f t="shared" ref="AG3:AG18" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
+        <f t="shared" ref="AG3:AG24" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF3)),TEXT(AF3,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH18" si="15">TEXT(I3,0)</f>
+        <f t="shared" ref="AH3:AH24" si="15">TEXT(I3,0)</f>
         <v>0</v>
       </c>
       <c r="AI3" t="str">
-        <f t="shared" ref="AI3:AI18" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
+        <f t="shared" ref="AI3:AI24" si="16">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH3)),TEXT(AH3,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ3">
@@ -8690,39 +8696,39 @@
         <v>1</v>
       </c>
       <c r="AK3" t="str">
-        <f t="shared" ref="AK3:AK18" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
+        <f t="shared" ref="AK3:AK24" si="17">CONCATENATE("[""FACTION""] = ",TEXT(AJ3,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL18" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
+        <f t="shared" ref="AL3:AL24" si="18">CONCATENATE("[""TIER""] = ",TEXT(M3,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM3" t="str">
-        <f t="shared" ref="AM3:AM18" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
+        <f t="shared" ref="AM3:AM24" si="19">IF(LEN(N3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N3)),"""",N3,"""; "),"")</f>
         <v xml:space="preserve">["MIN_LVL"] = "50"; </v>
       </c>
       <c r="AN3" t="str">
-        <f t="shared" ref="AN3:AN18" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
+        <f t="shared" ref="AN3:AN24" si="20">IF(LEN(O3)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O3)),"""",O3,"""; "),"")</f>
         <v/>
       </c>
       <c r="AO3" t="str">
-        <f t="shared" ref="AO3:AO18" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <f t="shared" ref="AO3:AO24" si="21">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Conquest of Dargazag"; }; </v>
       </c>
       <c r="AP3" t="str">
-        <f t="shared" ref="AP3:AP18" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
+        <f t="shared" ref="AP3:AP24" si="22">CONCATENATE("[""LORE""] = { [""EN""] = """,L3,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "The Enemy's forces in the field are led by a number of Chieftans. Defeating them all will weaken the morale of their forces, and deny them leadership."; }; </v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ18" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <f t="shared" ref="AQ3:AQ24" si="23">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K3,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Defeat 4 chieftains"; }; </v>
       </c>
       <c r="AR3" t="str">
-        <f t="shared" ref="AR3:AR18" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
+        <f t="shared" ref="AR3:AR24" si="24">IF(LEN(G3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G3,"""; }; "),"")</f>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Conqueror of Dargazag"; }; </v>
       </c>
       <c r="AS3" t="str">
-        <f t="shared" ref="AS3:AS22" si="25">CONCATENATE("};")</f>
+        <f t="shared" ref="AS3:AS24" si="25">CONCATENATE("};")</f>
         <v>};</v>
       </c>
     </row>
@@ -10637,11 +10643,11 @@
         <v>342</v>
       </c>
       <c r="R19" t="str">
-        <f t="shared" ref="R19:R22" si="26">CONCATENATE(U19,W19,X19,AS19," -- ",C19)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> [18] = {["CAT_ID"] = 342; }; -- - Season 6: Rivals -</v>
       </c>
       <c r="S19" s="1" t="str">
-        <f t="shared" ref="S19:S22" si="27">CONCATENATE(U19,V19,Y19,AA19,AC19,AE19,AG19,AI19,AK19,AL19,AM19,AN19,AO19,AP19,AQ19,AR19,AS19)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> [18] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 6: Rivals -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T19">
@@ -10649,23 +10655,23 @@
         <v>18</v>
       </c>
       <c r="U19" t="str">
-        <f t="shared" ref="U19:U22" si="28">CONCATENATE(REPT(" ",3-LEN(T19)),"[",T19,"] = {")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [18] = {</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" ref="V19:V22" si="29">IF(LEN(A19)&gt;0,CONCATENATE("[""ID""] = ",A19,"; "),"                     ")</f>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W19" t="str">
-        <f t="shared" ref="W19:W22" si="30">IF(LEN(A19)&gt;0,CONCATENATE("[""ID""] = ",A19,"; "),"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f t="shared" ref="X19:X22" si="31">IF(LEN(P19)&gt;0,CONCATENATE("[""CAT_ID""] = ",P19,"; "),"")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">["CAT_ID"] = 342; </v>
       </c>
       <c r="Y19" s="1" t="str">
-        <f t="shared" ref="Y19:Y22" si="32">IF(LEN(B19)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B19)),B19,"; "),REPT(" ",20))</f>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z19">
@@ -10673,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="AA19" t="str">
-        <f t="shared" ref="AA19:AA22" si="33">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z19)),Z19,"; ")</f>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB19" t="str">
@@ -10681,31 +10687,31 @@
         <v/>
       </c>
       <c r="AC19" t="str">
-        <f t="shared" ref="AC19:AC22" si="34">IF(NOT(ISBLANK(E19)),CONCATENATE("[""NA""] = ",AB19,"; "),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD19" t="str">
-        <f t="shared" ref="AD19:AD22" si="35">TEXT(F19,0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE19" t="str">
-        <f t="shared" ref="AE19:AE22" si="36">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD19)),TEXT(AD19,"0"),"; ")</f>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF19" t="str">
-        <f t="shared" ref="AF19:AF22" si="37">TEXT(H19,0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG19" t="str">
-        <f t="shared" ref="AG19:AG22" si="38">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF19)),TEXT(AF19,"0"),"; ")</f>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH19" t="str">
-        <f t="shared" ref="AH19:AH22" si="39">TEXT(I19,0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI19" t="str">
-        <f t="shared" ref="AI19:AI22" si="40">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH19)),TEXT(AH19,"0"),"; ")</f>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ19">
@@ -10713,35 +10719,35 @@
         <v>1</v>
       </c>
       <c r="AK19" t="str">
-        <f t="shared" ref="AK19:AK22" si="41">CONCATENATE("[""FACTION""] = ",TEXT(AJ19,"0"),"; ")</f>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL19" t="str">
-        <f t="shared" ref="AL19:AL22" si="42">CONCATENATE("[""TIER""] = ",TEXT(M19,"0"),"; ")</f>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM19" t="str">
-        <f t="shared" ref="AM19:AM22" si="43">IF(LEN(N19)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N19)),"""",N19,"""; "),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN19" t="str">
-        <f t="shared" ref="AN19:AN22" si="44">IF(LEN(O19)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O19)),"""",O19,"""; "),"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO19" t="str">
-        <f t="shared" ref="AO19:AO22" si="45">CONCATENATE("[""NAME""] = { [""EN""] = """,C19,"""; }; ")</f>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 6: Rivals -"; }; </v>
       </c>
       <c r="AP19" t="str">
-        <f t="shared" ref="AP19:AP22" si="46">CONCATENATE("[""LORE""] = { [""EN""] = """,L19,"""; }; ")</f>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ19" t="str">
-        <f t="shared" ref="AQ19:AQ22" si="47">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K19,"""; }; ")</f>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR19" t="str">
-        <f t="shared" ref="AR19:AR22" si="48">IF(LEN(G19)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G19,"""; }; "),"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS19" t="str">
@@ -10761,11 +10767,11 @@
       </c>
       <c r="N20" s="2"/>
       <c r="R20" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> [19] = {["ID"] = 1879523597; }; -- Title: Bastion of Light</v>
       </c>
       <c r="S20" s="1" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> [19] = {["ID"] = 1879523597;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Title: Bastion of Light"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T20">
@@ -10773,23 +10779,23 @@
         <v>19</v>
       </c>
       <c r="U20" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [19] = {</v>
       </c>
       <c r="V20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">["ID"] = 1879523597; </v>
       </c>
       <c r="W20" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">["ID"] = 1879523597; </v>
       </c>
       <c r="X20" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y20" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
       <c r="Z20">
@@ -10797,7 +10803,7 @@
         <v>7</v>
       </c>
       <c r="AA20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="AB20" t="str">
@@ -10805,31 +10811,31 @@
         <v/>
       </c>
       <c r="AC20" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD20" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE20" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG20" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH20" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI20" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ20">
@@ -10837,35 +10843,35 @@
         <v>1</v>
       </c>
       <c r="AK20" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL20" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM20" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN20" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO20" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Title: Bastion of Light"; }; </v>
       </c>
       <c r="AP20" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ20" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR20" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS20" t="str">
@@ -10874,78 +10880,86 @@
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D21" s="2"/>
+      <c r="C21" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="N21" s="2"/>
+      <c r="P21">
+        <v>349</v>
+      </c>
       <c r="R21" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [20] = {}; -- </v>
-      </c>
-      <c r="S21" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [20] = {["CAT_ID"] = 349; }; -- - Season 7: Destruction -</v>
+      </c>
+      <c r="S21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [20] = {                                         ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "- Season 7: Destruction -"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T21">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="U21" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [20] = {</v>
       </c>
       <c r="V21" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="W21" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="X21" t="str">
-        <f t="shared" si="31"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">["CAT_ID"] = 349; </v>
       </c>
       <c r="Y21" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z21" t="e">
+      <c r="Z21">
         <f>VLOOKUP(D21,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA21" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <v>14</v>
+      </c>
+      <c r="AA21" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB21" t="str">
         <f>IF(NOT(ISBLANK(E21)),VLOOKUP(E21,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC21" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD21" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE21" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF21" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG21" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH21" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI21" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ21">
@@ -10953,35 +10967,35 @@
         <v>1</v>
       </c>
       <c r="AK21" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL21" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM21" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN21" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO21" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "- Season 7: Destruction -"; }; </v>
       </c>
       <c r="AP21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ21" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR21" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS21" t="str">
@@ -10990,78 +11004,86 @@
       </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="D22" s="2"/>
+      <c r="A22">
+        <v>1879526227</v>
+      </c>
+      <c r="C22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D22" t="s">
+        <v>154</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="R22" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve"> [21] = {}; -- </v>
-      </c>
-      <c r="S22" s="1" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [21] = {["ID"] = 1879526227; }; -- Frame: Season of Destruction Frame</v>
+      </c>
+      <c r="S22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> [21] = {["ID"] = 1879526227;                     ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Frame: Season of Destruction Frame"; }; ["LORE"] = { ["EN"] = ""; }; ["SUMMARY"] = { ["EN"] = ""; }; };</v>
       </c>
       <c r="T22">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="U22" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> [21] = {</v>
       </c>
       <c r="V22" t="str">
-        <f t="shared" si="29"/>
-        <v xml:space="preserve">                     </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">["ID"] = 1879526227; </v>
       </c>
       <c r="W22" t="str">
-        <f t="shared" si="30"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">["ID"] = 1879526227; </v>
       </c>
       <c r="X22" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Y22" s="1" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">                    </v>
       </c>
-      <c r="Z22" t="e">
+      <c r="Z22">
         <f>VLOOKUP(D22,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA22" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <v>7</v>
+      </c>
+      <c r="AA22" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="AB22" t="str">
         <f>IF(NOT(ISBLANK(E22)),VLOOKUP(E22,[1]Type!D$2:E$6,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC22" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD22" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE22" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AF22" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG22" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AH22" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AJ22">
@@ -11069,35 +11091,35 @@
         <v>1</v>
       </c>
       <c r="AK22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AL22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AM22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AN22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AO22" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Frame: Season of Destruction Frame"; }; </v>
       </c>
       <c r="AP22" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AQ22" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AR22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AS22" t="str">
@@ -11108,13 +11130,233 @@
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="S23" s="1"/>
-      <c r="Y23" s="1"/>
+      <c r="R23" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [22] = {}; -- </v>
+      </c>
+      <c r="S23" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U23" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> [22] = {</v>
+      </c>
+      <c r="V23" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W23" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Y23" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="Z23" t="e">
+        <f>VLOOKUP(D23,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA23" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB23" t="str">
+        <f>IF(NOT(ISBLANK(E23)),VLOOKUP(E23,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF23" t="str">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH23" t="str">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI23" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ23">
+        <f>IF(NOT(ISBLANK(J23)),VLOOKUP(J23,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK23" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL23" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AM23" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AN23" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AO23" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP23" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AQ23" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AR23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AS23" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="N24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="Y24" s="1"/>
+      <c r="R24" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [23] = {}; -- </v>
+      </c>
+      <c r="S24" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="U24" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> [23] = {</v>
+      </c>
+      <c r="V24" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W24" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Y24" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="Z24" t="e">
+        <f>VLOOKUP(D24,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA24" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB24" t="str">
+        <f>IF(NOT(ISBLANK(E24)),VLOOKUP(E24,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD24" t="str">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF24" t="str">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH24" t="str">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI24" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ24">
+        <f>IF(NOT(ISBLANK(J24)),VLOOKUP(J24,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK24" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL24" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AM24" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AN24" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AO24" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP24" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AQ24" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AR24" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AS24" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="S25" s="1"/>

--- a/_SourceFiles/DeedInfo-4-The War.xlsx
+++ b/_SourceFiles/DeedInfo-4-The War.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02611CA2-B28A-4C02-A02B-361F40D261F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37192271-8CDC-46BA-AC8E-2A9A36DC3A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="480" windowWidth="17295" windowHeight="14430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="219">
   <si>
     <t>Save Index</t>
   </si>
@@ -678,6 +678,24 @@
   </si>
   <si>
     <t>- Season 7: Destruction -</t>
+  </si>
+  <si>
+    <t>Sorceress-slayer</t>
+  </si>
+  <si>
+    <t>Sorceress Slayer -- Tier 1</t>
+  </si>
+  <si>
+    <t>Sorceress Slayer -- Tier 3</t>
+  </si>
+  <si>
+    <t>Sorceress Slayer -- Tier 2</t>
+  </si>
+  <si>
+    <t>Sorceress Slayer -- Tier 5</t>
+  </si>
+  <si>
+    <t>Sorceress Slayer -- Tier 4</t>
   </si>
 </sst>
 </file>
@@ -1651,28 +1669,28 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1941,10 +1959,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS46"/>
+  <dimension ref="A1:AS56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="11" max="11" width="45.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
@@ -2243,7 +2262,7 @@
         <v>30</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R45" si="1">CONCATENATE(U3,W3,X3,AL3,AS3," -- ",C3)</f>
+        <f t="shared" ref="R3:R56" si="1">CONCATENATE(U3,W3,X3,AL3,AS3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879071804; }; -- Monster-slayer -- Tier 7</v>
       </c>
       <c r="S3" s="1" t="str">
@@ -2251,7 +2270,7 @@
         <v xml:space="preserve">  [2] = {["ID"] = 1879071804; ["SAVE_INDEX"] =  1; ["TYPE"] =  4; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["MIN_LVL"] = "30"; ["NAME"] = { ["EN"] = "Monster-slayer -- Tier 7"; }; ["LORE"] = { ["EN"] = "Stem the tides of Darkness in the War."; }; ["SUMMARY"] = { ["EN"] = "Defeat 50000 monster-players in the War"; }; ["TITLE"] = { ["EN"] = "Hero of Legend"; }; };</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T46" si="3">ROW()-1</f>
+        <f t="shared" ref="T3:T56" si="3">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="U3" t="str">
@@ -2351,7 +2370,7 @@
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Hero of Legend"; }; </v>
       </c>
       <c r="AS3" t="str">
-        <f t="shared" ref="AS3:AS46" si="25">CONCATENATE("};")</f>
+        <f t="shared" ref="AS3:AS56" si="25">CONCATENATE("};")</f>
         <v>};</v>
       </c>
     </row>
@@ -8175,9 +8194,22 @@
       </c>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="S46" s="1" t="e">
+      <c r="C46" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P46">
+        <v>350</v>
+      </c>
+      <c r="R46" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [45] = {["CAT_ID"] = 350; }; -- Sorceress-slayer</v>
+      </c>
+      <c r="S46" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
+        <v xml:space="preserve"> [45] = {                                          ["TYPE"] = 14; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1;                     ["NAME"] = { ["EN"] = "Sorceress-slayer"; }; };</v>
       </c>
       <c r="T46">
         <f t="shared" si="3"/>
@@ -8197,19 +8229,19 @@
       </c>
       <c r="X46" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v xml:space="preserve">["CAT_ID"] = 350; </v>
       </c>
       <c r="Y46" s="1" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">                     </v>
       </c>
-      <c r="Z46" t="e">
+      <c r="Z46">
         <f>VLOOKUP(D46,[1]Type!A$2:B$18,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA46" t="e">
+        <v>14</v>
+      </c>
+      <c r="AA46" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="AB46" t="str">
         <f>IF(NOT(ISBLANK(E46)),VLOOKUP(E46,[1]Type!D$2:E$6,2,FALSE),"")</f>
@@ -8265,7 +8297,7 @@
       </c>
       <c r="AO46" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress-slayer"; }; </v>
       </c>
       <c r="AP46" t="str">
         <f t="shared" si="22"/>
@@ -8280,6 +8312,1191 @@
         <v/>
       </c>
       <c r="AS46" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1879526544</v>
+      </c>
+      <c r="C47" t="s">
+        <v>217</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="R47" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [46] = {["ID"] = 1879526544; }; -- Sorceress Slayer -- Tier 5</v>
+      </c>
+      <c r="S47" s="1" t="e">
+        <f t="shared" ref="S47:S56" si="26">CONCATENATE(U47,V47,Y47,AA47,AC47,AE47,AG47,AI47,AK47,AL47,AM47,AN47,AO47,AP47,AQ47,AR47,AS47)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="U47" t="str">
+        <f t="shared" ref="U47:U56" si="27">CONCATENATE(REPT(" ",3-LEN(T47)),"[",T47,"] = {")</f>
+        <v xml:space="preserve"> [46] = {</v>
+      </c>
+      <c r="V47" t="str">
+        <f t="shared" ref="V47:V56" si="28">IF(LEN(A47)&gt;0,CONCATENATE("[""ID""] = ",A47,"; "),"                     ")</f>
+        <v xml:space="preserve">["ID"] = 1879526544; </v>
+      </c>
+      <c r="W47" t="str">
+        <f t="shared" ref="W47:W56" si="29">IF(LEN(A47)&gt;0,CONCATENATE("[""ID""] = ",A47,"; "),"")</f>
+        <v xml:space="preserve">["ID"] = 1879526544; </v>
+      </c>
+      <c r="X47" t="str">
+        <f t="shared" ref="X47:X56" si="30">IF(LEN(P47)&gt;0,CONCATENATE("[""CAT_ID""] = ",P47,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="Y47" s="1" t="str">
+        <f t="shared" ref="Y47:Y56" si="31">IF(LEN(B47)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",2-LEN(B47)),B47,"; "),REPT(" ",21))</f>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z47" t="e">
+        <f>VLOOKUP(D47,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA47" t="e">
+        <f t="shared" ref="AA47:AA56" si="32">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(Z47)),Z47,"; ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB47" t="str">
+        <f>IF(NOT(ISBLANK(E47)),VLOOKUP(E47,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC47" t="str">
+        <f t="shared" ref="AC47:AC56" si="33">IF(NOT(ISBLANK(E47)),CONCATENATE("[""NA""] = ",AB47,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="AD47" t="str">
+        <f t="shared" ref="AD47:AD56" si="34">TEXT(F47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE47" t="str">
+        <f t="shared" ref="AE47:AE56" si="35">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(AD47)),TEXT(AD47,"0"),"; ")</f>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF47" t="str">
+        <f t="shared" ref="AF47:AF56" si="36">TEXT(H47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG47" t="str">
+        <f t="shared" ref="AG47:AG56" si="37">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AF47)),TEXT(AF47,"0"),"; ")</f>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH47" t="str">
+        <f t="shared" ref="AH47:AH56" si="38">TEXT(I47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI47" t="str">
+        <f t="shared" ref="AI47:AI56" si="39">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AH47)),TEXT(AH47,"0"),"; ")</f>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ47">
+        <f>IF(NOT(ISBLANK(J47)),VLOOKUP(J47,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK47" t="str">
+        <f t="shared" ref="AK47:AK56" si="40">CONCATENATE("[""FACTION""] = ",TEXT(AJ47,"0"),"; ")</f>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL47" t="str">
+        <f t="shared" ref="AL47:AL56" si="41">IF(M47&gt;0,CONCATENATE("[""TIER""] = ",TEXT(M47,"0"),"; "),"")</f>
+        <v/>
+      </c>
+      <c r="AM47" t="str">
+        <f t="shared" ref="AM47:AM56" si="42">IF(LEN(N47)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",2-LEN(N47)),"""",N47,"""; "),"                    ")</f>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN47" t="str">
+        <f t="shared" ref="AN47:AN56" si="43">IF(LEN(O47)&gt;0,CONCATENATE("[""MIN_LVL""] = ",REPT(" ",3-LEN(O47)),"""",O47,"""; "),"")</f>
+        <v/>
+      </c>
+      <c r="AO47" t="str">
+        <f t="shared" ref="AO47:AO56" si="44">CONCATENATE("[""NAME""] = { [""EN""] = """,C47,"""; }; ")</f>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress Slayer -- Tier 5"; }; </v>
+      </c>
+      <c r="AP47" t="str">
+        <f t="shared" ref="AP47:AP56" si="45">IF(LEN(L47)&gt;0,CONCATENATE("[""LORE""] = { [""EN""] = """,L47,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AQ47" t="str">
+        <f t="shared" ref="AQ47:AQ56" si="46">IF(LEN(K47),CONCATENATE("[""SUMMARY""] = { [""EN""] = """,K47,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AR47" t="str">
+        <f t="shared" ref="AR47:AR56" si="47">IF(LEN(G47)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,G47,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AS47" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1879526545</v>
+      </c>
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="R48" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [47] = {["ID"] = 1879526545; ["TIER"] = 1; }; -- Sorceress Slayer -- Tier 4</v>
+      </c>
+      <c r="S48" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="U48" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [47] = {</v>
+      </c>
+      <c r="V48" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["ID"] = 1879526545; </v>
+      </c>
+      <c r="W48" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">["ID"] = 1879526545; </v>
+      </c>
+      <c r="X48" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y48" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z48" t="e">
+        <f>VLOOKUP(D48,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA48" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB48" t="str">
+        <f>IF(NOT(ISBLANK(E48)),VLOOKUP(E48,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC48" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD48" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE48" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF48" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG48" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH48" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI48" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ48">
+        <f>IF(NOT(ISBLANK(J48)),VLOOKUP(J48,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK48" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL48" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AM48" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN48" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO48" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress Slayer -- Tier 4"; }; </v>
+      </c>
+      <c r="AP48" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ48" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR48" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS48" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1879526533</v>
+      </c>
+      <c r="C49" t="s">
+        <v>215</v>
+      </c>
+      <c r="M49">
+        <v>2</v>
+      </c>
+      <c r="R49" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [48] = {["ID"] = 1879526533; ["TIER"] = 2; }; -- Sorceress Slayer -- Tier 3</v>
+      </c>
+      <c r="S49" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="U49" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [48] = {</v>
+      </c>
+      <c r="V49" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["ID"] = 1879526533; </v>
+      </c>
+      <c r="W49" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">["ID"] = 1879526533; </v>
+      </c>
+      <c r="X49" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y49" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z49" t="e">
+        <f>VLOOKUP(D49,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA49" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB49" t="str">
+        <f>IF(NOT(ISBLANK(E49)),VLOOKUP(E49,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC49" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD49" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE49" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF49" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG49" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH49" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI49" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ49">
+        <f>IF(NOT(ISBLANK(J49)),VLOOKUP(J49,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK49" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL49" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AM49" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN49" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO49" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress Slayer -- Tier 3"; }; </v>
+      </c>
+      <c r="AP49" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ49" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR49" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS49" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1879526534</v>
+      </c>
+      <c r="C50" t="s">
+        <v>216</v>
+      </c>
+      <c r="M50">
+        <v>3</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [49] = {["ID"] = 1879526534; ["TIER"] = 3; }; -- Sorceress Slayer -- Tier 2</v>
+      </c>
+      <c r="S50" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="U50" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [49] = {</v>
+      </c>
+      <c r="V50" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["ID"] = 1879526534; </v>
+      </c>
+      <c r="W50" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">["ID"] = 1879526534; </v>
+      </c>
+      <c r="X50" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y50" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z50" t="e">
+        <f>VLOOKUP(D50,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA50" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB50" t="str">
+        <f>IF(NOT(ISBLANK(E50)),VLOOKUP(E50,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC50" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD50" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE50" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF50" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG50" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH50" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI50" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ50">
+        <f>IF(NOT(ISBLANK(J50)),VLOOKUP(J50,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK50" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL50" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AM50" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN50" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO50" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress Slayer -- Tier 2"; }; </v>
+      </c>
+      <c r="AP50" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ50" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR50" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS50" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1879526532</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [50] = {["ID"] = 1879526532; ["TIER"] = 4; }; -- Sorceress Slayer -- Tier 1</v>
+      </c>
+      <c r="S51" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="U51" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [50] = {</v>
+      </c>
+      <c r="V51" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["ID"] = 1879526532; </v>
+      </c>
+      <c r="W51" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">["ID"] = 1879526532; </v>
+      </c>
+      <c r="X51" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y51" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z51" t="e">
+        <f>VLOOKUP(D51,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA51" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB51" t="str">
+        <f>IF(NOT(ISBLANK(E51)),VLOOKUP(E51,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC51" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD51" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE51" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF51" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG51" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH51" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI51" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ51">
+        <f>IF(NOT(ISBLANK(J51)),VLOOKUP(J51,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK51" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL51" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["TIER"] = 4; </v>
+      </c>
+      <c r="AM51" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN51" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO51" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Sorceress Slayer -- Tier 1"; }; </v>
+      </c>
+      <c r="AP51" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ51" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR51" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS51" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R52" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [51] = {}; -- </v>
+      </c>
+      <c r="S52" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="U52" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [51] = {</v>
+      </c>
+      <c r="V52" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W52" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X52" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y52" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z52" t="e">
+        <f>VLOOKUP(D52,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA52" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB52" t="str">
+        <f>IF(NOT(ISBLANK(E52)),VLOOKUP(E52,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC52" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD52" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE52" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF52" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG52" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH52" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI52" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ52">
+        <f>IF(NOT(ISBLANK(J52)),VLOOKUP(J52,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK52" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL52" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM52" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN52" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO52" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP52" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ52" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR52" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS52" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R53" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [52] = {}; -- </v>
+      </c>
+      <c r="S53" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="U53" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [52] = {</v>
+      </c>
+      <c r="V53" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W53" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X53" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y53" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z53" t="e">
+        <f>VLOOKUP(D53,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA53" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB53" t="str">
+        <f>IF(NOT(ISBLANK(E53)),VLOOKUP(E53,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC53" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD53" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE53" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF53" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG53" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH53" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI53" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ53">
+        <f>IF(NOT(ISBLANK(J53)),VLOOKUP(J53,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK53" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL53" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM53" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN53" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO53" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP53" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ53" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR53" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS53" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R54" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [53] = {}; -- </v>
+      </c>
+      <c r="S54" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="U54" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [53] = {</v>
+      </c>
+      <c r="V54" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W54" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X54" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y54" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z54" t="e">
+        <f>VLOOKUP(D54,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA54" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB54" t="str">
+        <f>IF(NOT(ISBLANK(E54)),VLOOKUP(E54,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC54" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD54" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE54" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF54" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG54" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH54" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI54" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ54">
+        <f>IF(NOT(ISBLANK(J54)),VLOOKUP(J54,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK54" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL54" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM54" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN54" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO54" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP54" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ54" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR54" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS54" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R55" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [54] = {}; -- </v>
+      </c>
+      <c r="S55" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="U55" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [54] = {</v>
+      </c>
+      <c r="V55" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W55" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X55" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y55" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z55" t="e">
+        <f>VLOOKUP(D55,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA55" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB55" t="str">
+        <f>IF(NOT(ISBLANK(E55)),VLOOKUP(E55,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC55" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD55" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE55" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF55" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG55" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH55" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI55" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ55">
+        <f>IF(NOT(ISBLANK(J55)),VLOOKUP(J55,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK55" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL55" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM55" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN55" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO55" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP55" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ55" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR55" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS55" t="str">
+        <f t="shared" si="25"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R56" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> [55] = {}; -- </v>
+      </c>
+      <c r="S56" s="1" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="U56" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve"> [55] = {</v>
+      </c>
+      <c r="V56" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="W56" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X56" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Y56" s="1" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="Z56" t="e">
+        <f>VLOOKUP(D56,[1]Type!A$2:B$18,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA56" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB56" t="str">
+        <f>IF(NOT(ISBLANK(E56)),VLOOKUP(E56,[1]Type!D$2:E$6,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="AC56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD56" t="str">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AE56" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AF56" t="str">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AG56" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AH56" t="str">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AI56" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AJ56">
+        <f>IF(NOT(ISBLANK(J56)),VLOOKUP(J56,[1]Faction!A$2:B$77,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AK56" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AL56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM56" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">                    </v>
+      </c>
+      <c r="AN56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AO56" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AP56" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ56" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AR56" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AS56" t="str">
         <f t="shared" si="25"/>
         <v>};</v>
       </c>
@@ -8291,7 +9508,7 @@
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P46">
+  <conditionalFormatting sqref="P2:P56">
     <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
